--- a/2026/BRIN 3219/Junio/BRIN3219-EXPENSAS-Junio.xlsx
+++ b/2026/BRIN 3219/Junio/BRIN3219-EXPENSAS-Junio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 3219\Mayo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BRIN 3219\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA23D9CC-4C77-4541-8401-185E1E4A0FAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE2DC69-8CA8-408F-BD1C-A27A119A3FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="27" r:id="rId1"/>
@@ -26,9 +26,6 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -498,31 +495,31 @@
     <t>Seguro - Reemplazo</t>
   </si>
   <si>
-    <t>VTO: 18/06</t>
-  </si>
-  <si>
-    <t>MAYO</t>
-  </si>
-  <si>
-    <t>Damato fumigaciones - MAYO</t>
-  </si>
-  <si>
-    <t>Egresos por gastos mes - MAYO</t>
-  </si>
-  <si>
-    <t>Mozart SRL  - recarga de matafuegos</t>
-  </si>
-  <si>
-    <t>Cuota 2 de 5 - Limpieza de columnas, cocina y baño de todas las unidades funcionales - Cuello Natalia</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reparacion Heredia - Trabajo integral proteccion contra roeadores, en sala de maquinas, medidores, cañerias y desagues - Limpiezas profundas, desinfeccion y retiruo de residuos </t>
-  </si>
-  <si>
     <t>Reclamo Juidicial  en sindicato por deuda que nos reclaman mal liquidada</t>
   </si>
   <si>
     <t>Acordarse de los -428650 en el resultado de la columna final de ingreso en prorrateo</t>
+  </si>
+  <si>
+    <t>VTO: 17/7</t>
+  </si>
+  <si>
+    <t>JUNIO</t>
+  </si>
+  <si>
+    <t>Damato fumigaciones - JUNIO</t>
+  </si>
+  <si>
+    <t>Egresos por gastos mes - JUNIO</t>
+  </si>
+  <si>
+    <t>Cuota 3 de 5 - Limpieza de columnas, cocina y baño de todas las unidades funcionales - Cuello Natalia</t>
+  </si>
+  <si>
+    <t>Facundo heredia - Cambio de lamparas, arme y desarme de plafon, reparacion de plafon de pasillo de entrada planta baja - Materiales y mano de obra</t>
+  </si>
+  <si>
+    <t>Articulos de limpieza</t>
   </si>
 </sst>
 </file>
@@ -1338,7 +1335,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="241">
+  <cellXfs count="245">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1635,6 +1632,109 @@
     <xf numFmtId="44" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1644,27 +1744,12 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1674,93 +1759,6 @@
     <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1797,7 +1795,16 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="44" fontId="30" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2245,16 +2252,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K99"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.7109375" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2269,23 +2276,23 @@
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="199"/>
-      <c r="E2" s="200"/>
-      <c r="F2" s="200"/>
-      <c r="G2" s="200"/>
-      <c r="H2" s="201"/>
+      <c r="D2" s="203"/>
+      <c r="E2" s="204"/>
+      <c r="F2" s="204"/>
+      <c r="G2" s="204"/>
+      <c r="H2" s="205"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10"/>
       <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="203">
+      <c r="E3" s="207">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="203"/>
-      <c r="G3" s="203"/>
-      <c r="H3" s="204"/>
+      <c r="F3" s="207"/>
+      <c r="G3" s="207"/>
+      <c r="H3" s="208"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10"/>
@@ -2321,7 +2328,7 @@
       <c r="A7" s="10"/>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="18.75">
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="18">
       <c r="A8" s="18" t="s">
         <v>5</v>
       </c>
@@ -2332,10 +2339,10 @@
         <v>66</v>
       </c>
       <c r="F8" s="89" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="H8" s="20"/>
     </row>
@@ -2364,14 +2371,14 @@
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="211"/>
-      <c r="B12" s="212"/>
-      <c r="C12" s="212"/>
-      <c r="D12" s="212"/>
-      <c r="E12" s="212"/>
-      <c r="F12" s="212"/>
-      <c r="G12" s="212"/>
-      <c r="H12" s="213"/>
+      <c r="A12" s="218"/>
+      <c r="B12" s="187"/>
+      <c r="C12" s="187"/>
+      <c r="D12" s="187"/>
+      <c r="E12" s="187"/>
+      <c r="F12" s="187"/>
+      <c r="G12" s="187"/>
+      <c r="H12" s="219"/>
     </row>
     <row r="13" spans="1:9" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
@@ -2383,17 +2390,17 @@
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:9" ht="15.75">
-      <c r="A14" s="214" t="s">
+    <row r="14" spans="1:9" ht="15.6">
+      <c r="A14" s="220" t="s">
         <v>121</v>
       </c>
-      <c r="B14" s="214"/>
-      <c r="C14" s="214"/>
-      <c r="D14" s="214"/>
-      <c r="E14" s="214"/>
-      <c r="F14" s="214"/>
-      <c r="G14" s="214"/>
-      <c r="H14" s="214"/>
+      <c r="B14" s="220"/>
+      <c r="C14" s="220"/>
+      <c r="D14" s="220"/>
+      <c r="E14" s="220"/>
+      <c r="F14" s="220"/>
+      <c r="G14" s="220"/>
+      <c r="H14" s="220"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="172" t="s">
@@ -2406,7 +2413,7 @@
       <c r="F15" s="137"/>
       <c r="G15" s="137"/>
       <c r="H15" s="73">
-        <v>358989.5</v>
+        <v>619789.12</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -2420,7 +2427,7 @@
       <c r="F16" s="137"/>
       <c r="G16" s="137"/>
       <c r="H16" s="73">
-        <v>-56540.84</v>
+        <v>-97616.78</v>
       </c>
       <c r="I16" s="7"/>
     </row>
@@ -2435,7 +2442,7 @@
       <c r="F17" s="137"/>
       <c r="G17" s="137"/>
       <c r="H17" s="73">
-        <v>0.34</v>
+        <v>0.66</v>
       </c>
       <c r="I17" s="7"/>
     </row>
@@ -2451,21 +2458,21 @@
       <c r="G18" s="137"/>
       <c r="H18" s="69">
         <f>SUM(H15:H17)</f>
-        <v>302449.00000000006</v>
+        <v>522172.99999999994</v>
       </c>
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" hidden="1">
-      <c r="A19" s="207" t="s">
+      <c r="A19" s="214" t="s">
         <v>138</v>
       </c>
-      <c r="B19" s="207"/>
-      <c r="C19" s="207"/>
-      <c r="D19" s="207"/>
-      <c r="E19" s="207"/>
-      <c r="F19" s="207"/>
-      <c r="G19" s="207"/>
-      <c r="H19" s="207"/>
+      <c r="B19" s="214"/>
+      <c r="C19" s="214"/>
+      <c r="D19" s="214"/>
+      <c r="E19" s="214"/>
+      <c r="F19" s="214"/>
+      <c r="G19" s="214"/>
+      <c r="H19" s="214"/>
     </row>
     <row r="20" spans="1:9" hidden="1">
       <c r="A20" s="172" t="s">
@@ -2511,16 +2518,16 @@
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="206" t="s">
+      <c r="A23" s="213" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="206"/>
-      <c r="C23" s="206"/>
-      <c r="D23" s="206"/>
-      <c r="E23" s="206"/>
-      <c r="F23" s="206"/>
-      <c r="G23" s="206"/>
-      <c r="H23" s="206"/>
+      <c r="B23" s="213"/>
+      <c r="C23" s="213"/>
+      <c r="D23" s="213"/>
+      <c r="E23" s="213"/>
+      <c r="F23" s="213"/>
+      <c r="G23" s="213"/>
+      <c r="H23" s="213"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="137" t="s">
@@ -2563,16 +2570,16 @@
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="202" t="s">
+      <c r="A27" s="206" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="202"/>
-      <c r="C27" s="202"/>
-      <c r="D27" s="202"/>
-      <c r="E27" s="202"/>
-      <c r="F27" s="202"/>
-      <c r="G27" s="202"/>
-      <c r="H27" s="202"/>
+      <c r="B27" s="206"/>
+      <c r="C27" s="206"/>
+      <c r="D27" s="206"/>
+      <c r="E27" s="206"/>
+      <c r="F27" s="206"/>
+      <c r="G27" s="206"/>
+      <c r="H27" s="206"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="172"/>
@@ -2594,9 +2601,9 @@
       <c r="E29" s="137"/>
       <c r="F29" s="137"/>
       <c r="G29" s="137"/>
-      <c r="H29" s="73">
-        <f>15645.63+1738.4+27787.31</f>
-        <v>45171.34</v>
+      <c r="H29" s="241">
+        <f>16154.53+1794.95+28729.76</f>
+        <v>46679.24</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -2625,20 +2632,20 @@
       <c r="G31" s="137"/>
       <c r="H31" s="69">
         <f>SUM(H28:H30)</f>
-        <v>45171.34</v>
+        <v>46679.24</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="202" t="s">
+      <c r="A32" s="206" t="s">
         <v>127</v>
       </c>
-      <c r="B32" s="202"/>
-      <c r="C32" s="202"/>
-      <c r="D32" s="202"/>
-      <c r="E32" s="202"/>
-      <c r="F32" s="202"/>
-      <c r="G32" s="202"/>
-      <c r="H32" s="202"/>
+      <c r="B32" s="206"/>
+      <c r="C32" s="206"/>
+      <c r="D32" s="206"/>
+      <c r="E32" s="206"/>
+      <c r="F32" s="206"/>
+      <c r="G32" s="206"/>
+      <c r="H32" s="206"/>
     </row>
     <row r="33" spans="1:11" ht="14.25" customHeight="1">
       <c r="A33" s="137" t="s">
@@ -2650,8 +2657,8 @@
       <c r="E33" s="137"/>
       <c r="F33" s="137"/>
       <c r="G33" s="137"/>
-      <c r="H33" s="73">
-        <v>467946.31</v>
+      <c r="H33" s="241">
+        <v>451922.84</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2664,8 +2671,8 @@
       <c r="E34" s="137"/>
       <c r="F34" s="137"/>
       <c r="G34" s="137"/>
-      <c r="H34" s="73">
-        <v>57718.38</v>
+      <c r="H34" s="241">
+        <v>61246.58</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2680,20 +2687,20 @@
       <c r="G35" s="137"/>
       <c r="H35" s="175">
         <f>SUM(H33:H34)</f>
-        <v>525664.68999999994</v>
+        <v>513169.42000000004</v>
       </c>
     </row>
     <row r="36" spans="1:11">
-      <c r="A36" s="214" t="s">
+      <c r="A36" s="220" t="s">
         <v>128</v>
       </c>
-      <c r="B36" s="214"/>
-      <c r="C36" s="214"/>
-      <c r="D36" s="214"/>
-      <c r="E36" s="214"/>
-      <c r="F36" s="214"/>
-      <c r="G36" s="214"/>
-      <c r="H36" s="214"/>
+      <c r="B36" s="220"/>
+      <c r="C36" s="220"/>
+      <c r="D36" s="220"/>
+      <c r="E36" s="220"/>
+      <c r="F36" s="220"/>
+      <c r="G36" s="220"/>
+      <c r="H36" s="220"/>
     </row>
     <row r="37" spans="1:11">
       <c r="A37" s="80" t="s">
@@ -2705,7 +2712,7 @@
       <c r="E37" s="137"/>
       <c r="F37" s="137"/>
       <c r="G37" s="137"/>
-      <c r="H37" s="73">
+      <c r="H37" s="241">
         <v>93200</v>
       </c>
     </row>
@@ -2719,23 +2726,24 @@
       <c r="E38" s="137"/>
       <c r="F38" s="137"/>
       <c r="G38" s="137"/>
-      <c r="H38" s="73">
-        <v>0</v>
+      <c r="H38" s="241">
+        <v>200000</v>
       </c>
       <c r="I38" s="7"/>
     </row>
-    <row r="39" spans="1:11" ht="36" customHeight="1">
-      <c r="A39" s="208" t="s">
-        <v>156</v>
-      </c>
-      <c r="B39" s="209"/>
-      <c r="C39" s="209"/>
-      <c r="D39" s="209"/>
-      <c r="E39" s="209"/>
-      <c r="F39" s="209"/>
-      <c r="G39" s="210"/>
-      <c r="H39" s="73">
-        <v>213000</v>
+    <row r="39" spans="1:11" ht="15.6" customHeight="1">
+      <c r="A39" s="215" t="s">
+        <v>158</v>
+      </c>
+      <c r="B39" s="216"/>
+      <c r="C39" s="216"/>
+      <c r="D39" s="216"/>
+      <c r="E39" s="216"/>
+      <c r="F39" s="216"/>
+      <c r="G39" s="217"/>
+      <c r="H39" s="241">
+        <f>71000+75400+57100</f>
+        <v>203500</v>
       </c>
       <c r="I39" s="7"/>
     </row>
@@ -2749,27 +2757,27 @@
       <c r="E40" s="137"/>
       <c r="F40" s="137"/>
       <c r="G40" s="137"/>
-      <c r="H40" s="73">
-        <v>26301.21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
-      <c r="A41" s="137" t="s">
-        <v>154</v>
-      </c>
-      <c r="B41" s="137"/>
-      <c r="C41" s="137"/>
-      <c r="D41" s="137"/>
-      <c r="E41" s="137"/>
-      <c r="F41" s="137"/>
-      <c r="G41" s="137"/>
-      <c r="H41" s="73">
-        <v>1783159.87</v>
+      <c r="H40" s="241">
+        <v>27686.79</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" ht="37.799999999999997" customHeight="1">
+      <c r="A41" s="242" t="s">
+        <v>157</v>
+      </c>
+      <c r="B41" s="243"/>
+      <c r="C41" s="243"/>
+      <c r="D41" s="243"/>
+      <c r="E41" s="243"/>
+      <c r="F41" s="243"/>
+      <c r="G41" s="244"/>
+      <c r="H41" s="241">
+        <v>55400</v>
       </c>
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="137" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="B42" s="137"/>
       <c r="C42" s="137"/>
@@ -2777,13 +2785,13 @@
       <c r="E42" s="137"/>
       <c r="F42" s="137"/>
       <c r="G42" s="137"/>
-      <c r="H42" s="73">
-        <v>65000</v>
+      <c r="H42" s="241">
+        <v>75000</v>
       </c>
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="137" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B43" s="137"/>
       <c r="C43" s="137"/>
@@ -2791,7 +2799,7 @@
       <c r="E43" s="137"/>
       <c r="F43" s="137"/>
       <c r="G43" s="137"/>
-      <c r="H43" s="73">
+      <c r="H43" s="241">
         <v>413700</v>
       </c>
     </row>
@@ -2807,20 +2815,20 @@
       <c r="G44" s="137"/>
       <c r="H44" s="69">
         <f>SUM(H37:H43)</f>
-        <v>2594361.08</v>
+        <v>1068486.79</v>
       </c>
     </row>
     <row r="45" spans="1:11">
-      <c r="A45" s="214" t="s">
+      <c r="A45" s="220" t="s">
         <v>129</v>
       </c>
-      <c r="B45" s="214"/>
-      <c r="C45" s="214"/>
-      <c r="D45" s="214"/>
-      <c r="E45" s="214"/>
-      <c r="F45" s="214"/>
-      <c r="G45" s="214"/>
-      <c r="H45" s="214"/>
+      <c r="B45" s="220"/>
+      <c r="C45" s="220"/>
+      <c r="D45" s="220"/>
+      <c r="E45" s="220"/>
+      <c r="F45" s="220"/>
+      <c r="G45" s="220"/>
+      <c r="H45" s="220"/>
     </row>
     <row r="46" spans="1:11">
       <c r="A46" s="137" t="s">
@@ -2870,16 +2878,16 @@
       <c r="K48" s="7"/>
     </row>
     <row r="49" spans="1:9" s="6" customFormat="1">
-      <c r="A49" s="186" t="s">
+      <c r="A49" s="221" t="s">
         <v>130</v>
       </c>
-      <c r="B49" s="187"/>
-      <c r="C49" s="187"/>
-      <c r="D49" s="187"/>
-      <c r="E49" s="187"/>
-      <c r="F49" s="187"/>
-      <c r="G49" s="187"/>
-      <c r="H49" s="188"/>
+      <c r="B49" s="222"/>
+      <c r="C49" s="222"/>
+      <c r="D49" s="222"/>
+      <c r="E49" s="222"/>
+      <c r="F49" s="222"/>
+      <c r="G49" s="222"/>
+      <c r="H49" s="223"/>
     </row>
     <row r="50" spans="1:9" s="6" customFormat="1">
       <c r="A50" s="80" t="s">
@@ -2891,8 +2899,8 @@
       <c r="E50" s="80"/>
       <c r="F50" s="80"/>
       <c r="G50" s="80"/>
-      <c r="H50" s="73">
-        <v>26307</v>
+      <c r="H50" s="241">
+        <v>28834</v>
       </c>
       <c r="I50" s="60"/>
     </row>
@@ -2908,24 +2916,24 @@
       <c r="G51" s="80"/>
       <c r="H51" s="69">
         <f>SUM(H50)</f>
-        <v>26307</v>
+        <v>28834</v>
       </c>
     </row>
     <row r="52" spans="1:9" s="6" customFormat="1">
-      <c r="A52" s="214" t="s">
+      <c r="A52" s="220" t="s">
         <v>131</v>
       </c>
-      <c r="B52" s="214"/>
-      <c r="C52" s="214"/>
-      <c r="D52" s="214"/>
-      <c r="E52" s="214"/>
-      <c r="F52" s="214"/>
-      <c r="G52" s="214"/>
-      <c r="H52" s="214"/>
+      <c r="B52" s="220"/>
+      <c r="C52" s="220"/>
+      <c r="D52" s="220"/>
+      <c r="E52" s="220"/>
+      <c r="F52" s="220"/>
+      <c r="G52" s="220"/>
+      <c r="H52" s="220"/>
     </row>
     <row r="53" spans="1:9" s="6" customFormat="1">
       <c r="A53" s="80" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="B53" s="80"/>
       <c r="C53" s="80"/>
@@ -2954,14 +2962,14 @@
       <c r="I54" s="60"/>
     </row>
     <row r="55" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A55" s="186"/>
-      <c r="B55" s="187"/>
-      <c r="C55" s="187"/>
-      <c r="D55" s="187"/>
-      <c r="E55" s="187"/>
-      <c r="F55" s="187"/>
-      <c r="G55" s="187"/>
-      <c r="H55" s="188"/>
+      <c r="A55" s="221"/>
+      <c r="B55" s="222"/>
+      <c r="C55" s="222"/>
+      <c r="D55" s="222"/>
+      <c r="E55" s="222"/>
+      <c r="F55" s="222"/>
+      <c r="G55" s="222"/>
+      <c r="H55" s="223"/>
     </row>
     <row r="56" spans="1:9" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
       <c r="A56" s="81"/>
@@ -3001,60 +3009,60 @@
       </c>
     </row>
     <row r="59" spans="1:9" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A59" s="192" t="s">
+      <c r="A59" s="224" t="s">
         <v>80</v>
       </c>
-      <c r="B59" s="193"/>
-      <c r="C59" s="193"/>
-      <c r="D59" s="193"/>
-      <c r="E59" s="193"/>
-      <c r="F59" s="193"/>
-      <c r="G59" s="193"/>
+      <c r="B59" s="225"/>
+      <c r="C59" s="225"/>
+      <c r="D59" s="225"/>
+      <c r="E59" s="225"/>
+      <c r="F59" s="225"/>
+      <c r="G59" s="225"/>
       <c r="H59" s="162">
         <f>H54</f>
         <v>80000</v>
       </c>
     </row>
     <row r="60" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A60" s="197"/>
-      <c r="B60" s="197"/>
-      <c r="C60" s="197"/>
-      <c r="D60" s="197"/>
-      <c r="E60" s="197"/>
-      <c r="F60" s="197"/>
-      <c r="G60" s="197"/>
-      <c r="H60" s="197"/>
+      <c r="A60" s="227"/>
+      <c r="B60" s="227"/>
+      <c r="C60" s="227"/>
+      <c r="D60" s="227"/>
+      <c r="E60" s="227"/>
+      <c r="F60" s="227"/>
+      <c r="G60" s="227"/>
+      <c r="H60" s="227"/>
     </row>
     <row r="61" spans="1:9" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A61" s="198"/>
-      <c r="B61" s="198"/>
-      <c r="C61" s="198"/>
-      <c r="D61" s="198"/>
-      <c r="E61" s="198"/>
-      <c r="F61" s="198"/>
-      <c r="G61" s="198"/>
-      <c r="H61" s="198"/>
+      <c r="A61" s="228"/>
+      <c r="B61" s="228"/>
+      <c r="C61" s="228"/>
+      <c r="D61" s="228"/>
+      <c r="E61" s="228"/>
+      <c r="F61" s="228"/>
+      <c r="G61" s="228"/>
+      <c r="H61" s="228"/>
     </row>
     <row r="62" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A62" s="196" t="s">
+      <c r="A62" s="226" t="s">
         <v>82</v>
       </c>
-      <c r="B62" s="196"/>
-      <c r="C62" s="196"/>
-      <c r="D62" s="196"/>
-      <c r="E62" s="196"/>
-      <c r="F62" s="196"/>
-      <c r="G62" s="196"/>
+      <c r="B62" s="226"/>
+      <c r="C62" s="226"/>
+      <c r="D62" s="226"/>
+      <c r="E62" s="226"/>
+      <c r="F62" s="226"/>
+      <c r="G62" s="226"/>
       <c r="H62" s="163"/>
     </row>
     <row r="63" spans="1:9" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A63" s="208"/>
-      <c r="B63" s="209"/>
-      <c r="C63" s="209"/>
-      <c r="D63" s="209"/>
-      <c r="E63" s="209"/>
-      <c r="F63" s="209"/>
-      <c r="G63" s="210"/>
+      <c r="A63" s="215"/>
+      <c r="B63" s="216"/>
+      <c r="C63" s="216"/>
+      <c r="D63" s="216"/>
+      <c r="E63" s="216"/>
+      <c r="F63" s="216"/>
+      <c r="G63" s="217"/>
       <c r="H63" s="73"/>
     </row>
     <row r="64" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
@@ -3098,30 +3106,30 @@
       </c>
     </row>
     <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A67" s="189" t="s">
+      <c r="A67" s="210" t="s">
         <v>87</v>
       </c>
-      <c r="B67" s="190"/>
-      <c r="C67" s="190"/>
-      <c r="D67" s="190"/>
-      <c r="E67" s="190"/>
-      <c r="F67" s="190"/>
-      <c r="G67" s="191"/>
+      <c r="B67" s="211"/>
+      <c r="C67" s="211"/>
+      <c r="D67" s="211"/>
+      <c r="E67" s="211"/>
+      <c r="F67" s="211"/>
+      <c r="G67" s="212"/>
       <c r="H67" s="130"/>
     </row>
     <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A68" s="189" t="s">
+      <c r="A68" s="210" t="s">
         <v>92</v>
       </c>
-      <c r="B68" s="190"/>
-      <c r="C68" s="190"/>
-      <c r="D68" s="190"/>
-      <c r="E68" s="190"/>
-      <c r="F68" s="190"/>
-      <c r="G68" s="191"/>
+      <c r="B68" s="211"/>
+      <c r="C68" s="211"/>
+      <c r="D68" s="211"/>
+      <c r="E68" s="211"/>
+      <c r="F68" s="211"/>
+      <c r="G68" s="212"/>
       <c r="H68" s="130"/>
     </row>
-    <row r="69" spans="1:11" ht="18.75">
+    <row r="69" spans="1:11" ht="18">
       <c r="A69" s="194" t="s">
         <v>88</v>
       </c>
@@ -3133,39 +3141,39 @@
       <c r="G69" s="195"/>
       <c r="H69" s="130">
         <f>H26+H35+H44+H48+H51+H31+H18+H22</f>
-        <v>3753153.11</v>
+        <v>2438542.4499999997</v>
       </c>
       <c r="J69" s="171"/>
       <c r="K69" s="142"/>
     </row>
-    <row r="70" spans="1:11" ht="18.75">
-      <c r="A70" s="225" t="s">
+    <row r="70" spans="1:11" ht="18">
+      <c r="A70" s="200" t="s">
         <v>119</v>
       </c>
-      <c r="B70" s="226"/>
-      <c r="C70" s="226"/>
-      <c r="D70" s="226"/>
-      <c r="E70" s="226"/>
-      <c r="F70" s="226"/>
-      <c r="G70" s="227"/>
+      <c r="B70" s="201"/>
+      <c r="C70" s="201"/>
+      <c r="D70" s="201"/>
+      <c r="E70" s="201"/>
+      <c r="F70" s="201"/>
+      <c r="G70" s="202"/>
       <c r="H70" s="131">
         <f>H67+H69</f>
-        <v>3753153.11</v>
+        <v>2438542.4499999997</v>
       </c>
       <c r="I70" s="126"/>
-      <c r="J70" s="205"/>
-      <c r="K70" s="205"/>
-    </row>
-    <row r="71" spans="1:11" ht="18.75">
-      <c r="A71" s="225" t="s">
+      <c r="J70" s="209"/>
+      <c r="K70" s="209"/>
+    </row>
+    <row r="71" spans="1:11" ht="18">
+      <c r="A71" s="200" t="s">
         <v>93</v>
       </c>
-      <c r="B71" s="226"/>
-      <c r="C71" s="226"/>
-      <c r="D71" s="226"/>
-      <c r="E71" s="226"/>
-      <c r="F71" s="226"/>
-      <c r="G71" s="227"/>
+      <c r="B71" s="201"/>
+      <c r="C71" s="201"/>
+      <c r="D71" s="201"/>
+      <c r="E71" s="201"/>
+      <c r="F71" s="201"/>
+      <c r="G71" s="202"/>
       <c r="H71" s="132">
         <f>H68+H66</f>
         <v>0</v>
@@ -3173,38 +3181,38 @@
       <c r="J71" s="142"/>
     </row>
     <row r="72" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A72" s="223" t="s">
+      <c r="A72" s="198" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="224"/>
-      <c r="C72" s="224"/>
-      <c r="D72" s="224"/>
-      <c r="E72" s="224"/>
-      <c r="F72" s="224"/>
-      <c r="G72" s="224"/>
+      <c r="B72" s="199"/>
+      <c r="C72" s="199"/>
+      <c r="D72" s="199"/>
+      <c r="E72" s="199"/>
+      <c r="F72" s="199"/>
+      <c r="G72" s="199"/>
       <c r="H72" s="133">
         <f>H69+H66</f>
-        <v>3753153.11</v>
+        <v>2438542.4499999997</v>
       </c>
       <c r="J72" s="7"/>
     </row>
-    <row r="73" spans="1:11" ht="18.75" hidden="1">
-      <c r="A73" s="221" t="s">
+    <row r="73" spans="1:11" ht="18" hidden="1">
+      <c r="A73" s="196" t="s">
         <v>17</v>
       </c>
-      <c r="B73" s="222"/>
-      <c r="C73" s="222"/>
-      <c r="D73" s="222"/>
-      <c r="E73" s="222"/>
-      <c r="F73" s="222"/>
-      <c r="G73" s="222"/>
+      <c r="B73" s="197"/>
+      <c r="C73" s="197"/>
+      <c r="D73" s="197"/>
+      <c r="E73" s="197"/>
+      <c r="F73" s="197"/>
+      <c r="G73" s="197"/>
       <c r="H73" s="134">
         <f>H58</f>
         <v>0</v>
       </c>
       <c r="J73" s="7"/>
     </row>
-    <row r="74" spans="1:11" ht="18.75" hidden="1">
+    <row r="74" spans="1:11" ht="18" hidden="1">
       <c r="A74" s="135"/>
       <c r="B74" s="135"/>
       <c r="C74" s="135"/>
@@ -3215,7 +3223,7 @@
       <c r="H74" s="136"/>
       <c r="J74" s="7"/>
     </row>
-    <row r="75" spans="1:11" ht="18.75" hidden="1">
+    <row r="75" spans="1:11" ht="18" hidden="1">
       <c r="A75" s="135"/>
       <c r="B75" s="135"/>
       <c r="C75" s="135"/>
@@ -3226,7 +3234,7 @@
       <c r="H75" s="136"/>
       <c r="J75" s="7"/>
     </row>
-    <row r="76" spans="1:11" ht="18.75" hidden="1">
+    <row r="76" spans="1:11" ht="18" hidden="1">
       <c r="A76" s="135"/>
       <c r="B76" s="135"/>
       <c r="C76" s="135"/>
@@ -3247,19 +3255,19 @@
       <c r="G77" s="137"/>
       <c r="H77" s="137"/>
     </row>
-    <row r="78" spans="1:11" ht="18.75">
-      <c r="A78" s="218" t="s">
+    <row r="78" spans="1:11" ht="18">
+      <c r="A78" s="191" t="s">
         <v>10</v>
       </c>
-      <c r="B78" s="219"/>
-      <c r="C78" s="219"/>
-      <c r="D78" s="219"/>
-      <c r="E78" s="219"/>
-      <c r="F78" s="219"/>
-      <c r="G78" s="219"/>
-      <c r="H78" s="220"/>
-    </row>
-    <row r="79" spans="1:11" ht="18.75">
+      <c r="B78" s="192"/>
+      <c r="C78" s="192"/>
+      <c r="D78" s="192"/>
+      <c r="E78" s="192"/>
+      <c r="F78" s="192"/>
+      <c r="G78" s="192"/>
+      <c r="H78" s="193"/>
+    </row>
+    <row r="79" spans="1:11" ht="18">
       <c r="A79" s="138" t="s">
         <v>12</v>
       </c>
@@ -3285,12 +3293,12 @@
       <c r="G80" s="82"/>
       <c r="H80" s="141">
         <f>Planilla!G32</f>
-        <v>1554352.4065020001</v>
+        <v>1564352.4065020001</v>
       </c>
     </row>
     <row r="81" spans="1:11">
       <c r="A81" s="78" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="B81" s="79"/>
       <c r="C81" s="79"/>
@@ -3300,7 +3308,7 @@
       <c r="G81" s="79"/>
       <c r="H81" s="179">
         <f>-(H72)</f>
-        <v>-3753153.11</v>
+        <v>-2438542.4499999997</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -3317,8 +3325,8 @@
         <f>-H59</f>
         <v>-80000</v>
       </c>
-      <c r="J82" s="240" t="s">
-        <v>158</v>
+      <c r="J82" s="186" t="s">
+        <v>151</v>
       </c>
       <c r="K82" s="6"/>
     </row>
@@ -3366,7 +3374,7 @@
       <c r="G85" s="4"/>
       <c r="H85" s="98"/>
     </row>
-    <row r="86" spans="1:11" ht="18.75">
+    <row r="86" spans="1:11" ht="18">
       <c r="A86" s="22" t="s">
         <v>11</v>
       </c>
@@ -3378,23 +3386,23 @@
       <c r="G86" s="23"/>
       <c r="H86" s="84">
         <f>SUM(H79:H85)</f>
-        <v>4724122.1164576914</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" ht="15.75" thickBot="1"/>
-    <row r="88" spans="1:11" ht="16.5" thickBot="1">
-      <c r="A88" s="215" t="s">
+        <v>6048732.7764576916</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" ht="15" thickBot="1"/>
+    <row r="88" spans="1:11" ht="16.2" thickBot="1">
+      <c r="A88" s="188" t="s">
         <v>97</v>
       </c>
-      <c r="B88" s="216"/>
-      <c r="C88" s="216"/>
-      <c r="D88" s="216"/>
-      <c r="E88" s="216"/>
-      <c r="F88" s="216"/>
-      <c r="G88" s="216"/>
-      <c r="H88" s="217"/>
-    </row>
-    <row r="89" spans="1:11" ht="15.75">
+      <c r="B88" s="189"/>
+      <c r="C88" s="189"/>
+      <c r="D88" s="189"/>
+      <c r="E88" s="189"/>
+      <c r="F88" s="189"/>
+      <c r="G88" s="189"/>
+      <c r="H88" s="190"/>
+    </row>
+    <row r="89" spans="1:11" ht="15.6">
       <c r="A89" s="87" t="s">
         <v>12</v>
       </c>
@@ -3456,55 +3464,54 @@
       </c>
     </row>
     <row r="96" spans="1:11" hidden="1">
-      <c r="A96" s="212"/>
-      <c r="B96" s="212"/>
-      <c r="C96" s="212"/>
-      <c r="D96" s="212"/>
-      <c r="E96" s="212"/>
-      <c r="F96" s="212"/>
-      <c r="G96" s="212"/>
-      <c r="H96" s="212"/>
+      <c r="A96" s="187"/>
+      <c r="B96" s="187"/>
+      <c r="C96" s="187"/>
+      <c r="D96" s="187"/>
+      <c r="E96" s="187"/>
+      <c r="F96" s="187"/>
+      <c r="G96" s="187"/>
+      <c r="H96" s="187"/>
     </row>
     <row r="97" spans="1:8" hidden="1">
-      <c r="A97" s="212"/>
-      <c r="B97" s="212"/>
-      <c r="C97" s="212"/>
-      <c r="D97" s="212"/>
-      <c r="E97" s="212"/>
-      <c r="F97" s="212"/>
-      <c r="G97" s="212"/>
-      <c r="H97" s="212"/>
+      <c r="A97" s="187"/>
+      <c r="B97" s="187"/>
+      <c r="C97" s="187"/>
+      <c r="D97" s="187"/>
+      <c r="E97" s="187"/>
+      <c r="F97" s="187"/>
+      <c r="G97" s="187"/>
+      <c r="H97" s="187"/>
     </row>
     <row r="98" spans="1:8" hidden="1">
-      <c r="A98" s="212"/>
-      <c r="B98" s="212"/>
-      <c r="C98" s="212"/>
-      <c r="D98" s="212"/>
-      <c r="E98" s="212"/>
-      <c r="F98" s="212"/>
-      <c r="G98" s="212"/>
-      <c r="H98" s="212"/>
+      <c r="A98" s="187"/>
+      <c r="B98" s="187"/>
+      <c r="C98" s="187"/>
+      <c r="D98" s="187"/>
+      <c r="E98" s="187"/>
+      <c r="F98" s="187"/>
+      <c r="G98" s="187"/>
+      <c r="H98" s="187"/>
     </row>
     <row r="99" spans="1:8" hidden="1">
-      <c r="A99" s="212"/>
-      <c r="B99" s="212"/>
-      <c r="C99" s="212"/>
-      <c r="D99" s="212"/>
-      <c r="E99" s="212"/>
-      <c r="F99" s="212"/>
-      <c r="G99" s="212"/>
-      <c r="H99" s="212"/>
+      <c r="A99" s="187"/>
+      <c r="B99" s="187"/>
+      <c r="C99" s="187"/>
+      <c r="D99" s="187"/>
+      <c r="E99" s="187"/>
+      <c r="F99" s="187"/>
+      <c r="G99" s="187"/>
+      <c r="H99" s="187"/>
     </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="A96:H99"/>
-    <mergeCell ref="A88:H88"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A70:G70"/>
+  <mergeCells count="31">
+    <mergeCell ref="A41:G41"/>
+    <mergeCell ref="A49:H49"/>
+    <mergeCell ref="A67:G67"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A66:G66"/>
+    <mergeCell ref="A62:G62"/>
+    <mergeCell ref="A60:H61"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="E3:H3"/>
@@ -3521,12 +3528,14 @@
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A45:H45"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="A62:G62"/>
-    <mergeCell ref="A60:H61"/>
+    <mergeCell ref="A96:H99"/>
+    <mergeCell ref="A88:H88"/>
+    <mergeCell ref="A78:H78"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A70:G70"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
@@ -3537,24 +3546,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" customWidth="1"/>
+    <col min="4" max="4" width="7.88671875" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.28515625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="2" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.5703125" style="2" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" customWidth="1"/>
+    <col min="11" max="11" width="10.5546875" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" customWidth="1"/>
+    <col min="14" max="14" width="13.44140625" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="26.25" customHeight="1">
@@ -3567,12 +3576,12 @@
       </c>
       <c r="F1" s="105" t="str">
         <f>RESUMEN!F8</f>
-        <v>MAYO</v>
+        <v>JUNIO</v>
       </c>
       <c r="G1" s="106"/>
       <c r="H1" s="104" t="str">
         <f>RESUMEN!G8</f>
-        <v>VTO: 18/06</v>
+        <v>VTO: 17/7</v>
       </c>
       <c r="I1" s="103"/>
       <c r="J1" s="103"/>
@@ -3650,16 +3659,16 @@
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="120"/>
-      <c r="B5" s="229">
+      <c r="B5" s="230">
         <f>C2</f>
         <v>3283892.26</v>
       </c>
-      <c r="C5" s="229"/>
+      <c r="C5" s="230"/>
       <c r="D5" s="21"/>
-      <c r="E5" s="235">
-        <v>0</v>
-      </c>
-      <c r="F5" s="236"/>
+      <c r="E5" s="236">
+        <v>0</v>
+      </c>
+      <c r="F5" s="237"/>
       <c r="G5" s="114"/>
       <c r="H5" s="114"/>
       <c r="I5" s="114"/>
@@ -3672,13 +3681,13 @@
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="120"/>
-      <c r="B6" s="231"/>
-      <c r="C6" s="232"/>
+      <c r="B6" s="232"/>
+      <c r="C6" s="233"/>
       <c r="D6" s="21"/>
-      <c r="E6" s="231" t="s">
+      <c r="E6" s="232" t="s">
         <v>146</v>
       </c>
-      <c r="F6" s="232"/>
+      <c r="F6" s="233"/>
       <c r="G6" s="114"/>
       <c r="H6" s="114"/>
       <c r="I6" s="114"/>
@@ -3691,11 +3700,11 @@
     </row>
     <row r="7" spans="1:17" ht="18.75" customHeight="1">
       <c r="A7" s="120"/>
-      <c r="B7" s="229"/>
-      <c r="C7" s="229"/>
+      <c r="B7" s="230"/>
+      <c r="C7" s="230"/>
       <c r="D7" s="21"/>
-      <c r="E7" s="233"/>
-      <c r="F7" s="234"/>
+      <c r="E7" s="234"/>
+      <c r="F7" s="235"/>
       <c r="G7" s="114"/>
       <c r="H7" s="114"/>
       <c r="I7" s="114"/>
@@ -4266,7 +4275,7 @@
       </c>
       <c r="G18" s="176">
         <f>25000+RESUMEN!H42+RESUMEN!H37</f>
-        <v>183200</v>
+        <v>193200</v>
       </c>
       <c r="H18" s="68">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
@@ -4278,7 +4287,7 @@
       </c>
       <c r="J18" s="68">
         <f t="shared" si="1"/>
-        <v>105318.47636508962</v>
+        <v>115318.47636508962</v>
       </c>
       <c r="K18" s="68">
         <f t="shared" si="2"/>
@@ -4298,7 +4307,7 @@
       </c>
       <c r="O18" s="183">
         <f t="shared" si="6"/>
-        <v>23120.101368910371</v>
+        <v>13120.101368910371</v>
       </c>
       <c r="Q18" s="180"/>
     </row>
@@ -5031,7 +5040,7 @@
         <v>148115.79716399999</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="15.75">
+    <row r="32" spans="1:18" ht="15.6">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -5049,7 +5058,7 @@
       </c>
       <c r="G32" s="99">
         <f>SUM(G9:G31)-428650</f>
-        <v>1554352.4065020001</v>
+        <v>1564352.4065020001</v>
       </c>
       <c r="H32" s="122">
         <f>SUM(H9:H31)</f>
@@ -5061,7 +5070,7 @@
       </c>
       <c r="J32" s="99">
         <f t="shared" ref="J32" si="8">SUM(J9:J31)</f>
-        <v>105318.47636508962</v>
+        <v>115318.47636508962</v>
       </c>
       <c r="K32" s="90">
         <f>SUM(K9:K31)</f>
@@ -5078,124 +5087,124 @@
       </c>
       <c r="O32" s="54">
         <f>SUM(O9:O31)</f>
-        <v>20562897.539019726</v>
+        <v>20552897.539019726</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="14.25" customHeight="1"/>
     <row r="34" spans="1:15" hidden="1">
-      <c r="B34" s="228"/>
-      <c r="C34" s="228"/>
-      <c r="D34" s="228"/>
-      <c r="E34" s="228"/>
-      <c r="F34" s="228"/>
-      <c r="G34" s="228"/>
-      <c r="H34" s="228"/>
-      <c r="I34" s="228"/>
-      <c r="J34" s="228"/>
-      <c r="K34" s="228"/>
-      <c r="L34" s="228"/>
-      <c r="M34" s="228"/>
-      <c r="N34" s="228"/>
-      <c r="O34" s="228"/>
+      <c r="B34" s="229"/>
+      <c r="C34" s="229"/>
+      <c r="D34" s="229"/>
+      <c r="E34" s="229"/>
+      <c r="F34" s="229"/>
+      <c r="G34" s="229"/>
+      <c r="H34" s="229"/>
+      <c r="I34" s="229"/>
+      <c r="J34" s="229"/>
+      <c r="K34" s="229"/>
+      <c r="L34" s="229"/>
+      <c r="M34" s="229"/>
+      <c r="N34" s="229"/>
+      <c r="O34" s="229"/>
     </row>
     <row r="35" spans="1:15" hidden="1">
-      <c r="B35" s="228"/>
-      <c r="C35" s="228"/>
-      <c r="D35" s="228"/>
-      <c r="E35" s="228"/>
-      <c r="F35" s="228"/>
-      <c r="G35" s="228"/>
-      <c r="H35" s="228"/>
-      <c r="I35" s="228"/>
-      <c r="J35" s="228"/>
-      <c r="K35" s="228"/>
-      <c r="L35" s="228"/>
-      <c r="M35" s="228"/>
-      <c r="N35" s="228"/>
-      <c r="O35" s="228"/>
+      <c r="B35" s="229"/>
+      <c r="C35" s="229"/>
+      <c r="D35" s="229"/>
+      <c r="E35" s="229"/>
+      <c r="F35" s="229"/>
+      <c r="G35" s="229"/>
+      <c r="H35" s="229"/>
+      <c r="I35" s="229"/>
+      <c r="J35" s="229"/>
+      <c r="K35" s="229"/>
+      <c r="L35" s="229"/>
+      <c r="M35" s="229"/>
+      <c r="N35" s="229"/>
+      <c r="O35" s="229"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
-      <c r="B36" s="228"/>
-      <c r="C36" s="228"/>
-      <c r="D36" s="228"/>
-      <c r="E36" s="228"/>
-      <c r="F36" s="228"/>
-      <c r="G36" s="228"/>
-      <c r="H36" s="228"/>
-      <c r="I36" s="228"/>
-      <c r="J36" s="228"/>
-      <c r="K36" s="228"/>
-      <c r="L36" s="228"/>
-      <c r="M36" s="228"/>
-      <c r="N36" s="228"/>
-      <c r="O36" s="228"/>
+      <c r="B36" s="229"/>
+      <c r="C36" s="229"/>
+      <c r="D36" s="229"/>
+      <c r="E36" s="229"/>
+      <c r="F36" s="229"/>
+      <c r="G36" s="229"/>
+      <c r="H36" s="229"/>
+      <c r="I36" s="229"/>
+      <c r="J36" s="229"/>
+      <c r="K36" s="229"/>
+      <c r="L36" s="229"/>
+      <c r="M36" s="229"/>
+      <c r="N36" s="229"/>
+      <c r="O36" s="229"/>
     </row>
     <row r="37" spans="1:15" hidden="1">
-      <c r="B37" s="228"/>
-      <c r="C37" s="228"/>
-      <c r="D37" s="228"/>
-      <c r="E37" s="228"/>
-      <c r="F37" s="228"/>
-      <c r="G37" s="228"/>
-      <c r="H37" s="228"/>
-      <c r="I37" s="228"/>
-      <c r="J37" s="228"/>
-      <c r="K37" s="228"/>
-      <c r="L37" s="228"/>
-      <c r="M37" s="228"/>
-      <c r="N37" s="228"/>
-      <c r="O37" s="228"/>
+      <c r="B37" s="229"/>
+      <c r="C37" s="229"/>
+      <c r="D37" s="229"/>
+      <c r="E37" s="229"/>
+      <c r="F37" s="229"/>
+      <c r="G37" s="229"/>
+      <c r="H37" s="229"/>
+      <c r="I37" s="229"/>
+      <c r="J37" s="229"/>
+      <c r="K37" s="229"/>
+      <c r="L37" s="229"/>
+      <c r="M37" s="229"/>
+      <c r="N37" s="229"/>
+      <c r="O37" s="229"/>
     </row>
     <row r="38" spans="1:15" hidden="1">
-      <c r="A38" s="230"/>
-      <c r="B38" s="230"/>
-      <c r="C38" s="230"/>
-      <c r="D38" s="230"/>
-      <c r="E38" s="230"/>
-      <c r="F38" s="230"/>
-      <c r="G38" s="230"/>
-      <c r="H38" s="230"/>
-      <c r="I38" s="230"/>
-      <c r="J38" s="230"/>
-      <c r="K38" s="230"/>
-      <c r="L38" s="230"/>
-      <c r="M38" s="230"/>
-      <c r="N38" s="230"/>
-      <c r="O38" s="230"/>
+      <c r="A38" s="231"/>
+      <c r="B38" s="231"/>
+      <c r="C38" s="231"/>
+      <c r="D38" s="231"/>
+      <c r="E38" s="231"/>
+      <c r="F38" s="231"/>
+      <c r="G38" s="231"/>
+      <c r="H38" s="231"/>
+      <c r="I38" s="231"/>
+      <c r="J38" s="231"/>
+      <c r="K38" s="231"/>
+      <c r="L38" s="231"/>
+      <c r="M38" s="231"/>
+      <c r="N38" s="231"/>
+      <c r="O38" s="231"/>
     </row>
     <row r="39" spans="1:15" hidden="1">
-      <c r="A39" s="230"/>
-      <c r="B39" s="230"/>
-      <c r="C39" s="230"/>
-      <c r="D39" s="230"/>
-      <c r="E39" s="230"/>
-      <c r="F39" s="230"/>
-      <c r="G39" s="230"/>
-      <c r="H39" s="230"/>
-      <c r="I39" s="230"/>
-      <c r="J39" s="230"/>
-      <c r="K39" s="230"/>
-      <c r="L39" s="230"/>
-      <c r="M39" s="230"/>
-      <c r="N39" s="230"/>
-      <c r="O39" s="230"/>
+      <c r="A39" s="231"/>
+      <c r="B39" s="231"/>
+      <c r="C39" s="231"/>
+      <c r="D39" s="231"/>
+      <c r="E39" s="231"/>
+      <c r="F39" s="231"/>
+      <c r="G39" s="231"/>
+      <c r="H39" s="231"/>
+      <c r="I39" s="231"/>
+      <c r="J39" s="231"/>
+      <c r="K39" s="231"/>
+      <c r="L39" s="231"/>
+      <c r="M39" s="231"/>
+      <c r="N39" s="231"/>
+      <c r="O39" s="231"/>
     </row>
     <row r="40" spans="1:15" hidden="1">
-      <c r="A40" s="230"/>
-      <c r="B40" s="230"/>
-      <c r="C40" s="230"/>
-      <c r="D40" s="230"/>
-      <c r="E40" s="230"/>
-      <c r="F40" s="230"/>
-      <c r="G40" s="230"/>
-      <c r="H40" s="230"/>
-      <c r="I40" s="230"/>
-      <c r="J40" s="230"/>
-      <c r="K40" s="230"/>
-      <c r="L40" s="230"/>
-      <c r="M40" s="230"/>
-      <c r="N40" s="230"/>
-      <c r="O40" s="230"/>
+      <c r="A40" s="231"/>
+      <c r="B40" s="231"/>
+      <c r="C40" s="231"/>
+      <c r="D40" s="231"/>
+      <c r="E40" s="231"/>
+      <c r="F40" s="231"/>
+      <c r="G40" s="231"/>
+      <c r="H40" s="231"/>
+      <c r="I40" s="231"/>
+      <c r="J40" s="231"/>
+      <c r="K40" s="231"/>
+      <c r="L40" s="231"/>
+      <c r="M40" s="231"/>
+      <c r="N40" s="231"/>
+      <c r="O40" s="231"/>
     </row>
     <row r="41" spans="1:15">
       <c r="O41" s="7"/>
@@ -5220,25 +5229,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.140625" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.109375" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="237" t="s">
+      <c r="A1" s="238" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="238"/>
-      <c r="C1" s="238"/>
-      <c r="D1" s="238"/>
-      <c r="E1" s="238"/>
-      <c r="F1" s="238"/>
-      <c r="G1" s="239"/>
+      <c r="B1" s="239"/>
+      <c r="C1" s="239"/>
+      <c r="D1" s="239"/>
+      <c r="E1" s="239"/>
+      <c r="F1" s="239"/>
+      <c r="G1" s="240"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="30"/>
@@ -5274,13 +5283,13 @@
       <c r="C6" s="16"/>
       <c r="G6" s="31"/>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1">
+    <row r="7" spans="1:7" ht="15" thickBot="1">
       <c r="A7" s="62"/>
       <c r="B7" s="32"/>
       <c r="C7" s="16"/>
       <c r="G7" s="31"/>
     </row>
-    <row r="8" spans="1:7" ht="30.75" thickBot="1">
+    <row r="8" spans="1:7" ht="29.4" thickBot="1">
       <c r="A8" s="26" t="s">
         <v>0</v>
       </c>
@@ -5641,7 +5650,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.75">
+    <row r="24" spans="1:7" ht="15.6">
       <c r="A24" s="51">
         <v>16</v>
       </c>
@@ -5663,7 +5672,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.75">
+    <row r="25" spans="1:7" ht="15.6">
       <c r="A25" s="51">
         <v>17</v>
       </c>
@@ -5685,7 +5694,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.75">
+    <row r="26" spans="1:7" ht="15.6">
       <c r="A26" s="51">
         <v>18</v>
       </c>
@@ -5707,7 +5716,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.75">
+    <row r="27" spans="1:7" ht="15.6">
       <c r="A27" s="51">
         <v>19</v>
       </c>
@@ -5733,7 +5742,7 @@
         <v>17603.28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.75">
+    <row r="28" spans="1:7" ht="15.6">
       <c r="A28" s="51">
         <v>20</v>
       </c>
@@ -5755,7 +5764,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.75">
+    <row r="29" spans="1:7" ht="15.6">
       <c r="A29" s="51">
         <v>21</v>
       </c>
@@ -5777,7 +5786,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.75">
+    <row r="30" spans="1:7" ht="15.6">
       <c r="A30" s="51">
         <v>22</v>
       </c>
@@ -5799,7 +5808,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.75">
+    <row r="31" spans="1:7" ht="15.6">
       <c r="A31" s="51">
         <v>23</v>
       </c>
@@ -5821,7 +5830,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.75">
+    <row r="32" spans="1:7" ht="15.6">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>

--- a/2026/BRIN 3219/Junio/BRIN3219-EXPENSAS-Junio.xlsx
+++ b/2026/BRIN 3219/Junio/BRIN3219-EXPENSAS-Junio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BRIN 3219\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 3219\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE2DC69-8CA8-408F-BD1C-A27A119A3FC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5C7752-547C-461D-B1D0-A21D596A641E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="27" r:id="rId1"/>
@@ -19,19 +19,22 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">Planilla!$A$1:$O$32</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$93</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$H$95</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="234" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="160">
   <si>
     <t>U.F.</t>
   </si>
@@ -495,12 +498,6 @@
     <t>Seguro - Reemplazo</t>
   </si>
   <si>
-    <t>Reclamo Juidicial  en sindicato por deuda que nos reclaman mal liquidada</t>
-  </si>
-  <si>
-    <t>Acordarse de los -428650 en el resultado de la columna final de ingreso en prorrateo</t>
-  </si>
-  <si>
     <t>VTO: 17/7</t>
   </si>
   <si>
@@ -520,6 +517,15 @@
   </si>
   <si>
     <t>Articulos de limpieza</t>
+  </si>
+  <si>
+    <t>MAM - Sistema de camaras</t>
+  </si>
+  <si>
+    <t>Honorarios Sr. Ezequiel Sarro - Abogado</t>
+  </si>
+  <si>
+    <t>Pago de convenio sindicato (abogado Maximiliano Nicolas Oliver Abogado del Sindicato para la apertura del pago de deuda de la cual estamos intimados)</t>
   </si>
 </sst>
 </file>
@@ -1335,7 +1341,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="245">
+  <cellXfs count="244">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
@@ -1632,7 +1638,6 @@
     <xf numFmtId="44" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1744,6 +1749,15 @@
     <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1795,16 +1809,7 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="30" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2251,17 +2256,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:K99"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <dimension ref="A1:K101"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="28.6640625" customWidth="1"/>
-    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" customWidth="1"/>
-    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.6640625" customWidth="1"/>
-    <col min="9" max="9" width="13.5546875" customWidth="1"/>
-    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" customWidth="1"/>
+    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.7109375" customWidth="1"/>
+    <col min="9" max="9" width="13.5703125" customWidth="1"/>
+    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2276,23 +2281,23 @@
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="203"/>
-      <c r="E2" s="204"/>
-      <c r="F2" s="204"/>
-      <c r="G2" s="204"/>
-      <c r="H2" s="205"/>
+      <c r="D2" s="202"/>
+      <c r="E2" s="203"/>
+      <c r="F2" s="203"/>
+      <c r="G2" s="203"/>
+      <c r="H2" s="204"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10"/>
       <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="207">
+      <c r="E3" s="206">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="207"/>
-      <c r="G3" s="207"/>
-      <c r="H3" s="208"/>
+      <c r="F3" s="206"/>
+      <c r="G3" s="206"/>
+      <c r="H3" s="207"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10"/>
@@ -2328,7 +2333,7 @@
       <c r="A7" s="10"/>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="18">
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="18.75">
       <c r="A8" s="18" t="s">
         <v>5</v>
       </c>
@@ -2339,10 +2344,10 @@
         <v>66</v>
       </c>
       <c r="F8" s="89" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G8" s="19" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="H8" s="20"/>
     </row>
@@ -2371,14 +2376,14 @@
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="218"/>
-      <c r="B12" s="187"/>
-      <c r="C12" s="187"/>
-      <c r="D12" s="187"/>
-      <c r="E12" s="187"/>
-      <c r="F12" s="187"/>
-      <c r="G12" s="187"/>
-      <c r="H12" s="219"/>
+      <c r="A12" s="217"/>
+      <c r="B12" s="186"/>
+      <c r="C12" s="186"/>
+      <c r="D12" s="186"/>
+      <c r="E12" s="186"/>
+      <c r="F12" s="186"/>
+      <c r="G12" s="186"/>
+      <c r="H12" s="218"/>
     </row>
     <row r="13" spans="1:9" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
@@ -2390,17 +2395,17 @@
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:9" ht="15.6">
-      <c r="A14" s="220" t="s">
+    <row r="14" spans="1:9" ht="15.75">
+      <c r="A14" s="219" t="s">
         <v>121</v>
       </c>
-      <c r="B14" s="220"/>
-      <c r="C14" s="220"/>
-      <c r="D14" s="220"/>
-      <c r="E14" s="220"/>
-      <c r="F14" s="220"/>
-      <c r="G14" s="220"/>
-      <c r="H14" s="220"/>
+      <c r="B14" s="219"/>
+      <c r="C14" s="219"/>
+      <c r="D14" s="219"/>
+      <c r="E14" s="219"/>
+      <c r="F14" s="219"/>
+      <c r="G14" s="219"/>
+      <c r="H14" s="219"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="172" t="s">
@@ -2463,16 +2468,16 @@
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" hidden="1">
-      <c r="A19" s="214" t="s">
+      <c r="A19" s="213" t="s">
         <v>138</v>
       </c>
-      <c r="B19" s="214"/>
-      <c r="C19" s="214"/>
-      <c r="D19" s="214"/>
-      <c r="E19" s="214"/>
-      <c r="F19" s="214"/>
-      <c r="G19" s="214"/>
-      <c r="H19" s="214"/>
+      <c r="B19" s="213"/>
+      <c r="C19" s="213"/>
+      <c r="D19" s="213"/>
+      <c r="E19" s="213"/>
+      <c r="F19" s="213"/>
+      <c r="G19" s="213"/>
+      <c r="H19" s="213"/>
     </row>
     <row r="20" spans="1:9" hidden="1">
       <c r="A20" s="172" t="s">
@@ -2518,16 +2523,16 @@
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="213" t="s">
+      <c r="A23" s="212" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="213"/>
-      <c r="C23" s="213"/>
-      <c r="D23" s="213"/>
-      <c r="E23" s="213"/>
-      <c r="F23" s="213"/>
-      <c r="G23" s="213"/>
-      <c r="H23" s="213"/>
+      <c r="B23" s="212"/>
+      <c r="C23" s="212"/>
+      <c r="D23" s="212"/>
+      <c r="E23" s="212"/>
+      <c r="F23" s="212"/>
+      <c r="G23" s="212"/>
+      <c r="H23" s="212"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="137" t="s">
@@ -2570,16 +2575,16 @@
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="206" t="s">
+      <c r="A27" s="205" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="206"/>
-      <c r="C27" s="206"/>
-      <c r="D27" s="206"/>
-      <c r="E27" s="206"/>
-      <c r="F27" s="206"/>
-      <c r="G27" s="206"/>
-      <c r="H27" s="206"/>
+      <c r="B27" s="205"/>
+      <c r="C27" s="205"/>
+      <c r="D27" s="205"/>
+      <c r="E27" s="205"/>
+      <c r="F27" s="205"/>
+      <c r="G27" s="205"/>
+      <c r="H27" s="205"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="172"/>
@@ -2601,7 +2606,7 @@
       <c r="E29" s="137"/>
       <c r="F29" s="137"/>
       <c r="G29" s="137"/>
-      <c r="H29" s="241">
+      <c r="H29" s="73">
         <f>16154.53+1794.95+28729.76</f>
         <v>46679.24</v>
       </c>
@@ -2636,18 +2641,18 @@
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="206" t="s">
+      <c r="A32" s="205" t="s">
         <v>127</v>
       </c>
-      <c r="B32" s="206"/>
-      <c r="C32" s="206"/>
-      <c r="D32" s="206"/>
-      <c r="E32" s="206"/>
-      <c r="F32" s="206"/>
-      <c r="G32" s="206"/>
-      <c r="H32" s="206"/>
-    </row>
-    <row r="33" spans="1:11" ht="14.25" customHeight="1">
+      <c r="B32" s="205"/>
+      <c r="C32" s="205"/>
+      <c r="D32" s="205"/>
+      <c r="E32" s="205"/>
+      <c r="F32" s="205"/>
+      <c r="G32" s="205"/>
+      <c r="H32" s="205"/>
+    </row>
+    <row r="33" spans="1:10" ht="14.25" customHeight="1">
       <c r="A33" s="137" t="s">
         <v>136</v>
       </c>
@@ -2657,11 +2662,11 @@
       <c r="E33" s="137"/>
       <c r="F33" s="137"/>
       <c r="G33" s="137"/>
-      <c r="H33" s="241">
-        <v>451922.84</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+      <c r="H33" s="73">
+        <v>446100.75</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" s="174" t="s">
         <v>98</v>
       </c>
@@ -2671,11 +2676,11 @@
       <c r="E34" s="137"/>
       <c r="F34" s="137"/>
       <c r="G34" s="137"/>
-      <c r="H34" s="241">
+      <c r="H34" s="73">
         <v>61246.58</v>
       </c>
     </row>
-    <row r="35" spans="1:11">
+    <row r="35" spans="1:10">
       <c r="A35" s="137" t="s">
         <v>73</v>
       </c>
@@ -2687,22 +2692,22 @@
       <c r="G35" s="137"/>
       <c r="H35" s="175">
         <f>SUM(H33:H34)</f>
-        <v>513169.42000000004</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
-      <c r="A36" s="220" t="s">
+        <v>507347.33</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="219" t="s">
         <v>128</v>
       </c>
-      <c r="B36" s="220"/>
-      <c r="C36" s="220"/>
-      <c r="D36" s="220"/>
-      <c r="E36" s="220"/>
-      <c r="F36" s="220"/>
-      <c r="G36" s="220"/>
-      <c r="H36" s="220"/>
-    </row>
-    <row r="37" spans="1:11">
+      <c r="B36" s="219"/>
+      <c r="C36" s="219"/>
+      <c r="D36" s="219"/>
+      <c r="E36" s="219"/>
+      <c r="F36" s="219"/>
+      <c r="G36" s="219"/>
+      <c r="H36" s="219"/>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" s="80" t="s">
         <v>68</v>
       </c>
@@ -2712,11 +2717,11 @@
       <c r="E37" s="137"/>
       <c r="F37" s="137"/>
       <c r="G37" s="137"/>
-      <c r="H37" s="241">
+      <c r="H37" s="73">
         <v>93200</v>
       </c>
     </row>
-    <row r="38" spans="1:11">
+    <row r="38" spans="1:10">
       <c r="A38" s="80" t="s">
         <v>143</v>
       </c>
@@ -2726,28 +2731,28 @@
       <c r="E38" s="137"/>
       <c r="F38" s="137"/>
       <c r="G38" s="137"/>
-      <c r="H38" s="241">
+      <c r="H38" s="73">
         <v>200000</v>
       </c>
       <c r="I38" s="7"/>
     </row>
-    <row r="39" spans="1:11" ht="15.6" customHeight="1">
-      <c r="A39" s="215" t="s">
-        <v>158</v>
-      </c>
-      <c r="B39" s="216"/>
-      <c r="C39" s="216"/>
-      <c r="D39" s="216"/>
-      <c r="E39" s="216"/>
-      <c r="F39" s="216"/>
-      <c r="G39" s="217"/>
-      <c r="H39" s="241">
+    <row r="39" spans="1:10" ht="15.6" customHeight="1">
+      <c r="A39" s="214" t="s">
+        <v>156</v>
+      </c>
+      <c r="B39" s="215"/>
+      <c r="C39" s="215"/>
+      <c r="D39" s="215"/>
+      <c r="E39" s="215"/>
+      <c r="F39" s="215"/>
+      <c r="G39" s="216"/>
+      <c r="H39" s="73">
         <f>71000+75400+57100</f>
         <v>203500</v>
       </c>
       <c r="I39" s="7"/>
     </row>
-    <row r="40" spans="1:11">
+    <row r="40" spans="1:10">
       <c r="A40" s="137" t="s">
         <v>69</v>
       </c>
@@ -2757,41 +2762,41 @@
       <c r="E40" s="137"/>
       <c r="F40" s="137"/>
       <c r="G40" s="137"/>
-      <c r="H40" s="241">
+      <c r="H40" s="73">
         <v>27686.79</v>
       </c>
     </row>
-    <row r="41" spans="1:11" ht="37.799999999999997" customHeight="1">
-      <c r="A41" s="242" t="s">
+    <row r="41" spans="1:10">
+      <c r="A41" s="81" t="s">
         <v>157</v>
       </c>
-      <c r="B41" s="243"/>
-      <c r="C41" s="243"/>
-      <c r="D41" s="243"/>
-      <c r="E41" s="243"/>
-      <c r="F41" s="243"/>
-      <c r="G41" s="244"/>
-      <c r="H41" s="241">
+      <c r="B41" s="82"/>
+      <c r="C41" s="82"/>
+      <c r="D41" s="82"/>
+      <c r="E41" s="82"/>
+      <c r="F41" s="82"/>
+      <c r="G41" s="243"/>
+      <c r="H41" s="73">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10" ht="37.9" customHeight="1">
+      <c r="A42" s="223" t="s">
+        <v>155</v>
+      </c>
+      <c r="B42" s="224"/>
+      <c r="C42" s="224"/>
+      <c r="D42" s="224"/>
+      <c r="E42" s="224"/>
+      <c r="F42" s="224"/>
+      <c r="G42" s="225"/>
+      <c r="H42" s="73">
         <v>55400</v>
       </c>
     </row>
-    <row r="42" spans="1:11">
-      <c r="A42" s="137" t="s">
-        <v>154</v>
-      </c>
-      <c r="B42" s="137"/>
-      <c r="C42" s="137"/>
-      <c r="D42" s="137"/>
-      <c r="E42" s="137"/>
-      <c r="F42" s="137"/>
-      <c r="G42" s="137"/>
-      <c r="H42" s="241">
-        <v>75000</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+    <row r="43" spans="1:10">
       <c r="A43" s="137" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="B43" s="137"/>
       <c r="C43" s="137"/>
@@ -2799,13 +2804,13 @@
       <c r="E43" s="137"/>
       <c r="F43" s="137"/>
       <c r="G43" s="137"/>
-      <c r="H43" s="241">
-        <v>413700</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+      <c r="H43" s="73">
+        <v>75000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" s="137" t="s">
-        <v>73</v>
+        <v>154</v>
       </c>
       <c r="B44" s="137"/>
       <c r="C44" s="137"/>
@@ -2813,43 +2818,40 @@
       <c r="E44" s="137"/>
       <c r="F44" s="137"/>
       <c r="G44" s="137"/>
-      <c r="H44" s="69">
-        <f>SUM(H37:H43)</f>
-        <v>1068486.79</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
-      <c r="A45" s="220" t="s">
+      <c r="H44" s="73">
+        <v>413700</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="137" t="s">
+        <v>73</v>
+      </c>
+      <c r="B45" s="137"/>
+      <c r="C45" s="137"/>
+      <c r="D45" s="137"/>
+      <c r="E45" s="137"/>
+      <c r="F45" s="137"/>
+      <c r="G45" s="137"/>
+      <c r="H45" s="69">
+        <f>SUM(H37:H44)</f>
+        <v>1113486.79</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="219" t="s">
         <v>129</v>
       </c>
-      <c r="B45" s="220"/>
-      <c r="C45" s="220"/>
-      <c r="D45" s="220"/>
-      <c r="E45" s="220"/>
-      <c r="F45" s="220"/>
-      <c r="G45" s="220"/>
-      <c r="H45" s="220"/>
-    </row>
-    <row r="46" spans="1:11">
-      <c r="A46" s="137" t="s">
+      <c r="B46" s="219"/>
+      <c r="C46" s="219"/>
+      <c r="D46" s="219"/>
+      <c r="E46" s="219"/>
+      <c r="F46" s="219"/>
+      <c r="G46" s="219"/>
+      <c r="H46" s="219"/>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="137" t="s">
         <v>70</v>
-      </c>
-      <c r="B46" s="137"/>
-      <c r="C46" s="137"/>
-      <c r="D46" s="137"/>
-      <c r="E46" s="137"/>
-      <c r="F46" s="137"/>
-      <c r="G46" s="137"/>
-      <c r="H46" s="73">
-        <v>189700</v>
-      </c>
-      <c r="J46" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
-      <c r="A47" s="137" t="s">
-        <v>114</v>
       </c>
       <c r="B47" s="137"/>
       <c r="C47" s="137"/>
@@ -2858,12 +2860,15 @@
       <c r="F47" s="137"/>
       <c r="G47" s="137"/>
       <c r="H47" s="73">
-        <v>45000</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+        <v>189700</v>
+      </c>
+      <c r="J47" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" s="137" t="s">
-        <v>72</v>
+        <v>114</v>
       </c>
       <c r="B48" s="137"/>
       <c r="C48" s="137"/>
@@ -2871,42 +2876,41 @@
       <c r="E48" s="137"/>
       <c r="F48" s="137"/>
       <c r="G48" s="137"/>
-      <c r="H48" s="175">
-        <f>SUM(H46:H47)</f>
+      <c r="H48" s="73">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
+      <c r="A49" s="137" t="s">
+        <v>72</v>
+      </c>
+      <c r="B49" s="137"/>
+      <c r="C49" s="137"/>
+      <c r="D49" s="137"/>
+      <c r="E49" s="137"/>
+      <c r="F49" s="137"/>
+      <c r="G49" s="137"/>
+      <c r="H49" s="175">
+        <f>SUM(H47:H48)</f>
         <v>234700</v>
       </c>
-      <c r="K48" s="7"/>
-    </row>
-    <row r="49" spans="1:9" s="6" customFormat="1">
-      <c r="A49" s="221" t="s">
+      <c r="K49" s="7"/>
+    </row>
+    <row r="50" spans="1:11" s="6" customFormat="1">
+      <c r="A50" s="220" t="s">
         <v>130</v>
       </c>
-      <c r="B49" s="222"/>
-      <c r="C49" s="222"/>
-      <c r="D49" s="222"/>
-      <c r="E49" s="222"/>
-      <c r="F49" s="222"/>
-      <c r="G49" s="222"/>
-      <c r="H49" s="223"/>
-    </row>
-    <row r="50" spans="1:9" s="6" customFormat="1">
-      <c r="A50" s="80" t="s">
+      <c r="B50" s="221"/>
+      <c r="C50" s="221"/>
+      <c r="D50" s="221"/>
+      <c r="E50" s="221"/>
+      <c r="F50" s="221"/>
+      <c r="G50" s="221"/>
+      <c r="H50" s="222"/>
+    </row>
+    <row r="51" spans="1:11" s="6" customFormat="1">
+      <c r="A51" s="80" t="s">
         <v>116</v>
-      </c>
-      <c r="B50" s="80"/>
-      <c r="C50" s="80"/>
-      <c r="D50" s="80"/>
-      <c r="E50" s="80"/>
-      <c r="F50" s="80"/>
-      <c r="G50" s="80"/>
-      <c r="H50" s="241">
-        <v>28834</v>
-      </c>
-      <c r="I50" s="60"/>
-    </row>
-    <row r="51" spans="1:9" s="6" customFormat="1">
-      <c r="A51" s="80" t="s">
-        <v>73</v>
       </c>
       <c r="B51" s="80"/>
       <c r="C51" s="80"/>
@@ -2914,40 +2918,41 @@
       <c r="E51" s="80"/>
       <c r="F51" s="80"/>
       <c r="G51" s="80"/>
-      <c r="H51" s="69">
-        <f>SUM(H50)</f>
+      <c r="H51" s="73">
         <v>28834</v>
       </c>
-    </row>
-    <row r="52" spans="1:9" s="6" customFormat="1">
-      <c r="A52" s="220" t="s">
+      <c r="I51" s="60"/>
+    </row>
+    <row r="52" spans="1:11" s="6" customFormat="1">
+      <c r="A52" s="80" t="s">
+        <v>73</v>
+      </c>
+      <c r="B52" s="80"/>
+      <c r="C52" s="80"/>
+      <c r="D52" s="80"/>
+      <c r="E52" s="80"/>
+      <c r="F52" s="80"/>
+      <c r="G52" s="80"/>
+      <c r="H52" s="69">
+        <f>SUM(H51)</f>
+        <v>28834</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" s="6" customFormat="1">
+      <c r="A53" s="219" t="s">
         <v>131</v>
       </c>
-      <c r="B52" s="220"/>
-      <c r="C52" s="220"/>
-      <c r="D52" s="220"/>
-      <c r="E52" s="220"/>
-      <c r="F52" s="220"/>
-      <c r="G52" s="220"/>
-      <c r="H52" s="220"/>
-    </row>
-    <row r="53" spans="1:9" s="6" customFormat="1">
-      <c r="A53" s="80" t="s">
-        <v>150</v>
-      </c>
-      <c r="B53" s="80"/>
-      <c r="C53" s="80"/>
-      <c r="D53" s="80"/>
-      <c r="E53" s="80"/>
-      <c r="F53" s="80"/>
-      <c r="G53" s="80"/>
-      <c r="H53" s="73">
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" s="6" customFormat="1" ht="15" customHeight="1">
+      <c r="B53" s="219"/>
+      <c r="C53" s="219"/>
+      <c r="D53" s="219"/>
+      <c r="E53" s="219"/>
+      <c r="F53" s="219"/>
+      <c r="G53" s="219"/>
+      <c r="H53" s="219"/>
+    </row>
+    <row r="54" spans="1:11" s="6" customFormat="1">
       <c r="A54" s="80" t="s">
-        <v>74</v>
+        <v>158</v>
       </c>
       <c r="B54" s="80"/>
       <c r="C54" s="80"/>
@@ -2955,286 +2960,295 @@
       <c r="E54" s="80"/>
       <c r="F54" s="80"/>
       <c r="G54" s="80"/>
-      <c r="H54" s="69">
-        <f>SUM(H53:H53)</f>
-        <v>80000</v>
-      </c>
-      <c r="I54" s="60"/>
-    </row>
-    <row r="55" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A55" s="221"/>
-      <c r="B55" s="222"/>
-      <c r="C55" s="222"/>
-      <c r="D55" s="222"/>
-      <c r="E55" s="222"/>
-      <c r="F55" s="222"/>
-      <c r="G55" s="222"/>
-      <c r="H55" s="223"/>
-    </row>
-    <row r="56" spans="1:9" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
-      <c r="A56" s="81"/>
-      <c r="B56" s="82"/>
-      <c r="C56" s="82"/>
-      <c r="D56" s="82"/>
-      <c r="E56" s="82"/>
-      <c r="F56" s="82"/>
-      <c r="G56" s="82"/>
-      <c r="H56" s="156">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
-      <c r="A57" s="157"/>
-      <c r="B57" s="158"/>
-      <c r="C57" s="158"/>
-      <c r="D57" s="158"/>
-      <c r="E57" s="158"/>
-      <c r="F57" s="158"/>
-      <c r="G57" s="158"/>
-      <c r="H57" s="159">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A58" s="160"/>
-      <c r="B58" s="161"/>
-      <c r="C58" s="161"/>
-      <c r="D58" s="161"/>
-      <c r="E58" s="161"/>
-      <c r="F58" s="161"/>
-      <c r="G58" s="161"/>
+      <c r="H54" s="73">
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" s="6" customFormat="1" ht="31.5" customHeight="1">
+      <c r="A55" s="214" t="s">
+        <v>159</v>
+      </c>
+      <c r="B55" s="215"/>
+      <c r="C55" s="215"/>
+      <c r="D55" s="215"/>
+      <c r="E55" s="215"/>
+      <c r="F55" s="215"/>
+      <c r="G55" s="216"/>
+      <c r="H55" s="73">
+        <v>997000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" s="6" customFormat="1" ht="15" customHeight="1">
+      <c r="A56" s="80" t="s">
+        <v>74</v>
+      </c>
+      <c r="B56" s="80"/>
+      <c r="C56" s="80"/>
+      <c r="D56" s="80"/>
+      <c r="E56" s="80"/>
+      <c r="F56" s="80"/>
+      <c r="G56" s="80"/>
+      <c r="H56" s="69">
+        <f>SUM(H54:H55)</f>
+        <v>1097000</v>
+      </c>
+      <c r="I56" s="60"/>
+    </row>
+    <row r="57" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A57" s="220"/>
+      <c r="B57" s="221"/>
+      <c r="C57" s="221"/>
+      <c r="D57" s="221"/>
+      <c r="E57" s="221"/>
+      <c r="F57" s="221"/>
+      <c r="G57" s="221"/>
+      <c r="H57" s="222"/>
+    </row>
+    <row r="58" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
+      <c r="A58" s="81"/>
+      <c r="B58" s="82"/>
+      <c r="C58" s="82"/>
+      <c r="D58" s="82"/>
+      <c r="E58" s="82"/>
+      <c r="F58" s="82"/>
+      <c r="G58" s="82"/>
       <c r="H58" s="156">
-        <f>H56+H57</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A59" s="224" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" s="6" customFormat="1" ht="20.25" hidden="1" customHeight="1">
+      <c r="A59" s="157"/>
+      <c r="B59" s="158"/>
+      <c r="C59" s="158"/>
+      <c r="D59" s="158"/>
+      <c r="E59" s="158"/>
+      <c r="F59" s="158"/>
+      <c r="G59" s="158"/>
+      <c r="H59" s="159">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A60" s="160"/>
+      <c r="B60" s="161"/>
+      <c r="C60" s="161"/>
+      <c r="D60" s="161"/>
+      <c r="E60" s="161"/>
+      <c r="F60" s="161"/>
+      <c r="G60" s="161"/>
+      <c r="H60" s="156">
+        <f>H58+H59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
+      <c r="A61" s="226" t="s">
         <v>80</v>
       </c>
-      <c r="B59" s="225"/>
-      <c r="C59" s="225"/>
-      <c r="D59" s="225"/>
-      <c r="E59" s="225"/>
-      <c r="F59" s="225"/>
-      <c r="G59" s="225"/>
-      <c r="H59" s="162">
-        <f>H54</f>
-        <v>80000</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A60" s="227"/>
-      <c r="B60" s="227"/>
-      <c r="C60" s="227"/>
-      <c r="D60" s="227"/>
-      <c r="E60" s="227"/>
-      <c r="F60" s="227"/>
-      <c r="G60" s="227"/>
-      <c r="H60" s="227"/>
-    </row>
-    <row r="61" spans="1:9" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A61" s="228"/>
-      <c r="B61" s="228"/>
-      <c r="C61" s="228"/>
-      <c r="D61" s="228"/>
-      <c r="E61" s="228"/>
-      <c r="F61" s="228"/>
-      <c r="G61" s="228"/>
-      <c r="H61" s="228"/>
-    </row>
-    <row r="62" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A62" s="226" t="s">
+      <c r="B61" s="227"/>
+      <c r="C61" s="227"/>
+      <c r="D61" s="227"/>
+      <c r="E61" s="227"/>
+      <c r="F61" s="227"/>
+      <c r="G61" s="227"/>
+      <c r="H61" s="162">
+        <f>H56</f>
+        <v>1097000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A62" s="229"/>
+      <c r="B62" s="229"/>
+      <c r="C62" s="229"/>
+      <c r="D62" s="229"/>
+      <c r="E62" s="229"/>
+      <c r="F62" s="229"/>
+      <c r="G62" s="229"/>
+      <c r="H62" s="229"/>
+    </row>
+    <row r="63" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
+      <c r="A63" s="230"/>
+      <c r="B63" s="230"/>
+      <c r="C63" s="230"/>
+      <c r="D63" s="230"/>
+      <c r="E63" s="230"/>
+      <c r="F63" s="230"/>
+      <c r="G63" s="230"/>
+      <c r="H63" s="230"/>
+    </row>
+    <row r="64" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A64" s="228" t="s">
         <v>82</v>
       </c>
-      <c r="B62" s="226"/>
-      <c r="C62" s="226"/>
-      <c r="D62" s="226"/>
-      <c r="E62" s="226"/>
-      <c r="F62" s="226"/>
-      <c r="G62" s="226"/>
-      <c r="H62" s="163"/>
-    </row>
-    <row r="63" spans="1:9" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A63" s="215"/>
-      <c r="B63" s="216"/>
-      <c r="C63" s="216"/>
-      <c r="D63" s="216"/>
-      <c r="E63" s="216"/>
-      <c r="F63" s="216"/>
-      <c r="G63" s="217"/>
-      <c r="H63" s="73"/>
-    </row>
-    <row r="64" spans="1:9" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A64" s="127" t="s">
+      <c r="B64" s="228"/>
+      <c r="C64" s="228"/>
+      <c r="D64" s="228"/>
+      <c r="E64" s="228"/>
+      <c r="F64" s="228"/>
+      <c r="G64" s="228"/>
+      <c r="H64" s="163"/>
+    </row>
+    <row r="65" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A65" s="214"/>
+      <c r="B65" s="215"/>
+      <c r="C65" s="215"/>
+      <c r="D65" s="215"/>
+      <c r="E65" s="215"/>
+      <c r="F65" s="215"/>
+      <c r="G65" s="216"/>
+      <c r="H65" s="73"/>
+    </row>
+    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
+      <c r="A66" s="127" t="s">
         <v>73</v>
       </c>
-      <c r="B64" s="80"/>
-      <c r="C64" s="80"/>
-      <c r="D64" s="80"/>
-      <c r="E64" s="80"/>
-      <c r="F64" s="80"/>
-      <c r="G64" s="80"/>
-      <c r="H64" s="69">
-        <f>SUM(H63:H63)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A65" s="128"/>
-      <c r="B65" s="128"/>
-      <c r="C65" s="128"/>
-      <c r="D65" s="128"/>
-      <c r="E65" s="128"/>
-      <c r="F65" s="128"/>
-      <c r="G65" s="128"/>
-      <c r="H65" s="129"/>
-    </row>
-    <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A66" s="194" t="s">
+      <c r="B66" s="80"/>
+      <c r="C66" s="80"/>
+      <c r="D66" s="80"/>
+      <c r="E66" s="80"/>
+      <c r="F66" s="80"/>
+      <c r="G66" s="80"/>
+      <c r="H66" s="69">
+        <f>SUM(H65:H65)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A67" s="128"/>
+      <c r="B67" s="128"/>
+      <c r="C67" s="128"/>
+      <c r="D67" s="128"/>
+      <c r="E67" s="128"/>
+      <c r="F67" s="128"/>
+      <c r="G67" s="128"/>
+      <c r="H67" s="129"/>
+    </row>
+    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A68" s="193" t="s">
         <v>81</v>
       </c>
-      <c r="B66" s="195"/>
-      <c r="C66" s="195"/>
-      <c r="D66" s="195"/>
-      <c r="E66" s="195"/>
-      <c r="F66" s="195"/>
-      <c r="G66" s="195"/>
-      <c r="H66" s="130">
-        <f>H64</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A67" s="210" t="s">
+      <c r="B68" s="194"/>
+      <c r="C68" s="194"/>
+      <c r="D68" s="194"/>
+      <c r="E68" s="194"/>
+      <c r="F68" s="194"/>
+      <c r="G68" s="194"/>
+      <c r="H68" s="130">
+        <f>H66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A69" s="209" t="s">
         <v>87</v>
       </c>
-      <c r="B67" s="211"/>
-      <c r="C67" s="211"/>
-      <c r="D67" s="211"/>
-      <c r="E67" s="211"/>
-      <c r="F67" s="211"/>
-      <c r="G67" s="212"/>
-      <c r="H67" s="130"/>
-    </row>
-    <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A68" s="210" t="s">
+      <c r="B69" s="210"/>
+      <c r="C69" s="210"/>
+      <c r="D69" s="210"/>
+      <c r="E69" s="210"/>
+      <c r="F69" s="210"/>
+      <c r="G69" s="211"/>
+      <c r="H69" s="130">
+        <f>3283892.26-2477720.36</f>
+        <v>806171.89999999991</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
+      <c r="A70" s="209" t="s">
         <v>92</v>
       </c>
-      <c r="B68" s="211"/>
-      <c r="C68" s="211"/>
-      <c r="D68" s="211"/>
-      <c r="E68" s="211"/>
-      <c r="F68" s="211"/>
-      <c r="G68" s="212"/>
-      <c r="H68" s="130"/>
-    </row>
-    <row r="69" spans="1:11" ht="18">
-      <c r="A69" s="194" t="s">
+      <c r="B70" s="210"/>
+      <c r="C70" s="210"/>
+      <c r="D70" s="210"/>
+      <c r="E70" s="210"/>
+      <c r="F70" s="210"/>
+      <c r="G70" s="211"/>
+      <c r="H70" s="130"/>
+    </row>
+    <row r="71" spans="1:11" ht="18.75">
+      <c r="A71" s="193" t="s">
         <v>88</v>
       </c>
-      <c r="B69" s="195"/>
-      <c r="C69" s="195"/>
-      <c r="D69" s="195"/>
-      <c r="E69" s="195"/>
-      <c r="F69" s="195"/>
-      <c r="G69" s="195"/>
-      <c r="H69" s="130">
-        <f>H26+H35+H44+H48+H51+H31+H18+H22</f>
-        <v>2438542.4499999997</v>
-      </c>
-      <c r="J69" s="171"/>
-      <c r="K69" s="142"/>
-    </row>
-    <row r="70" spans="1:11" ht="18">
-      <c r="A70" s="200" t="s">
+      <c r="B71" s="194"/>
+      <c r="C71" s="194"/>
+      <c r="D71" s="194"/>
+      <c r="E71" s="194"/>
+      <c r="F71" s="194"/>
+      <c r="G71" s="194"/>
+      <c r="H71" s="130">
+        <f>H26+H35+H45+H49+H52+H31+H18+H22</f>
+        <v>2477720.36</v>
+      </c>
+      <c r="J71" s="171"/>
+      <c r="K71" s="142"/>
+    </row>
+    <row r="72" spans="1:11" ht="18.75">
+      <c r="A72" s="199" t="s">
         <v>119</v>
       </c>
-      <c r="B70" s="201"/>
-      <c r="C70" s="201"/>
-      <c r="D70" s="201"/>
-      <c r="E70" s="201"/>
-      <c r="F70" s="201"/>
-      <c r="G70" s="202"/>
-      <c r="H70" s="131">
-        <f>H67+H69</f>
-        <v>2438542.4499999997</v>
-      </c>
-      <c r="I70" s="126"/>
-      <c r="J70" s="209"/>
-      <c r="K70" s="209"/>
-    </row>
-    <row r="71" spans="1:11" ht="18">
-      <c r="A71" s="200" t="s">
+      <c r="B72" s="200"/>
+      <c r="C72" s="200"/>
+      <c r="D72" s="200"/>
+      <c r="E72" s="200"/>
+      <c r="F72" s="200"/>
+      <c r="G72" s="201"/>
+      <c r="H72" s="131">
+        <f>H69+H71</f>
+        <v>3283892.26</v>
+      </c>
+      <c r="I72" s="126"/>
+      <c r="J72" s="208"/>
+      <c r="K72" s="208"/>
+    </row>
+    <row r="73" spans="1:11" ht="18.75">
+      <c r="A73" s="199" t="s">
         <v>93</v>
       </c>
-      <c r="B71" s="201"/>
-      <c r="C71" s="201"/>
-      <c r="D71" s="201"/>
-      <c r="E71" s="201"/>
-      <c r="F71" s="201"/>
-      <c r="G71" s="202"/>
-      <c r="H71" s="132">
-        <f>H68+H66</f>
-        <v>0</v>
-      </c>
-      <c r="J71" s="142"/>
-    </row>
-    <row r="72" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A72" s="198" t="s">
+      <c r="B73" s="200"/>
+      <c r="C73" s="200"/>
+      <c r="D73" s="200"/>
+      <c r="E73" s="200"/>
+      <c r="F73" s="200"/>
+      <c r="G73" s="201"/>
+      <c r="H73" s="132">
+        <f>H70+H68</f>
+        <v>0</v>
+      </c>
+      <c r="J73" s="142"/>
+    </row>
+    <row r="74" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
+      <c r="A74" s="197" t="s">
         <v>83</v>
       </c>
-      <c r="B72" s="199"/>
-      <c r="C72" s="199"/>
-      <c r="D72" s="199"/>
-      <c r="E72" s="199"/>
-      <c r="F72" s="199"/>
-      <c r="G72" s="199"/>
-      <c r="H72" s="133">
-        <f>H69+H66</f>
-        <v>2438542.4499999997</v>
-      </c>
-      <c r="J72" s="7"/>
-    </row>
-    <row r="73" spans="1:11" ht="18" hidden="1">
-      <c r="A73" s="196" t="s">
+      <c r="B74" s="198"/>
+      <c r="C74" s="198"/>
+      <c r="D74" s="198"/>
+      <c r="E74" s="198"/>
+      <c r="F74" s="198"/>
+      <c r="G74" s="198"/>
+      <c r="H74" s="133">
+        <f>H71+H68</f>
+        <v>2477720.36</v>
+      </c>
+      <c r="J74" s="7"/>
+    </row>
+    <row r="75" spans="1:11" ht="18.75" hidden="1">
+      <c r="A75" s="195" t="s">
         <v>17</v>
       </c>
-      <c r="B73" s="197"/>
-      <c r="C73" s="197"/>
-      <c r="D73" s="197"/>
-      <c r="E73" s="197"/>
-      <c r="F73" s="197"/>
-      <c r="G73" s="197"/>
-      <c r="H73" s="134">
-        <f>H58</f>
-        <v>0</v>
-      </c>
-      <c r="J73" s="7"/>
-    </row>
-    <row r="74" spans="1:11" ht="18" hidden="1">
-      <c r="A74" s="135"/>
-      <c r="B74" s="135"/>
-      <c r="C74" s="135"/>
-      <c r="D74" s="135"/>
-      <c r="E74" s="135"/>
-      <c r="F74" s="135"/>
-      <c r="G74" s="135"/>
-      <c r="H74" s="136"/>
-      <c r="J74" s="7"/>
-    </row>
-    <row r="75" spans="1:11" ht="18" hidden="1">
-      <c r="A75" s="135"/>
-      <c r="B75" s="135"/>
-      <c r="C75" s="135"/>
-      <c r="D75" s="135"/>
-      <c r="E75" s="135"/>
-      <c r="F75" s="135"/>
-      <c r="G75" s="135"/>
-      <c r="H75" s="136"/>
+      <c r="B75" s="196"/>
+      <c r="C75" s="196"/>
+      <c r="D75" s="196"/>
+      <c r="E75" s="196"/>
+      <c r="F75" s="196"/>
+      <c r="G75" s="196"/>
+      <c r="H75" s="134">
+        <f>H60</f>
+        <v>0</v>
+      </c>
       <c r="J75" s="7"/>
     </row>
-    <row r="76" spans="1:11" ht="18" hidden="1">
+    <row r="76" spans="1:11" ht="18.75" hidden="1">
       <c r="A76" s="135"/>
       <c r="B76" s="135"/>
       <c r="C76" s="135"/>
@@ -3245,94 +3259,82 @@
       <c r="H76" s="136"/>
       <c r="J76" s="7"/>
     </row>
-    <row r="77" spans="1:11" ht="14.25" customHeight="1">
-      <c r="A77" s="137"/>
-      <c r="B77" s="137"/>
-      <c r="C77" s="137"/>
-      <c r="D77" s="137"/>
-      <c r="E77" s="137"/>
-      <c r="F77" s="137"/>
-      <c r="G77" s="137"/>
-      <c r="H77" s="137"/>
-    </row>
-    <row r="78" spans="1:11" ht="18">
-      <c r="A78" s="191" t="s">
+    <row r="77" spans="1:11" ht="18.75" hidden="1">
+      <c r="A77" s="135"/>
+      <c r="B77" s="135"/>
+      <c r="C77" s="135"/>
+      <c r="D77" s="135"/>
+      <c r="E77" s="135"/>
+      <c r="F77" s="135"/>
+      <c r="G77" s="135"/>
+      <c r="H77" s="136"/>
+      <c r="J77" s="7"/>
+    </row>
+    <row r="78" spans="1:11" ht="18.75" hidden="1">
+      <c r="A78" s="135"/>
+      <c r="B78" s="135"/>
+      <c r="C78" s="135"/>
+      <c r="D78" s="135"/>
+      <c r="E78" s="135"/>
+      <c r="F78" s="135"/>
+      <c r="G78" s="135"/>
+      <c r="H78" s="136"/>
+      <c r="J78" s="7"/>
+    </row>
+    <row r="79" spans="1:11" ht="14.25" customHeight="1">
+      <c r="A79" s="137"/>
+      <c r="B79" s="137"/>
+      <c r="C79" s="137"/>
+      <c r="D79" s="137"/>
+      <c r="E79" s="137"/>
+      <c r="F79" s="137"/>
+      <c r="G79" s="137"/>
+      <c r="H79" s="137"/>
+    </row>
+    <row r="80" spans="1:11" ht="18.75">
+      <c r="A80" s="190" t="s">
         <v>10</v>
       </c>
-      <c r="B78" s="192"/>
-      <c r="C78" s="192"/>
-      <c r="D78" s="192"/>
-      <c r="E78" s="192"/>
-      <c r="F78" s="192"/>
-      <c r="G78" s="192"/>
-      <c r="H78" s="193"/>
-    </row>
-    <row r="79" spans="1:11" ht="18">
-      <c r="A79" s="138" t="s">
+      <c r="B80" s="191"/>
+      <c r="C80" s="191"/>
+      <c r="D80" s="191"/>
+      <c r="E80" s="191"/>
+      <c r="F80" s="191"/>
+      <c r="G80" s="191"/>
+      <c r="H80" s="192"/>
+    </row>
+    <row r="81" spans="1:11" ht="18.75">
+      <c r="A81" s="138" t="s">
         <v>12</v>
       </c>
-      <c r="B79" s="139"/>
-      <c r="C79" s="139"/>
-      <c r="D79" s="139"/>
-      <c r="E79" s="139"/>
-      <c r="F79" s="139"/>
-      <c r="G79" s="139"/>
-      <c r="H79" s="140">
-        <v>6822922.8199556917</v>
-      </c>
-    </row>
-    <row r="80" spans="1:11">
-      <c r="A80" s="81" t="s">
+      <c r="B81" s="139"/>
+      <c r="C81" s="139"/>
+      <c r="D81" s="139"/>
+      <c r="E81" s="139"/>
+      <c r="F81" s="139"/>
+      <c r="G81" s="139"/>
+      <c r="H81" s="140">
+        <v>4724122.12</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" s="81" t="s">
         <v>145</v>
       </c>
-      <c r="B80" s="82"/>
-      <c r="C80" s="82"/>
-      <c r="D80" s="82"/>
-      <c r="E80" s="82"/>
-      <c r="F80" s="82"/>
-      <c r="G80" s="82"/>
-      <c r="H80" s="141">
+      <c r="B82" s="82"/>
+      <c r="C82" s="82"/>
+      <c r="D82" s="82"/>
+      <c r="E82" s="82"/>
+      <c r="F82" s="82"/>
+      <c r="G82" s="82"/>
+      <c r="H82" s="141">
         <f>Planilla!G32</f>
-        <v>1564352.4065020001</v>
-      </c>
-    </row>
-    <row r="81" spans="1:11">
-      <c r="A81" s="78" t="s">
-        <v>155</v>
-      </c>
-      <c r="B81" s="79"/>
-      <c r="C81" s="79"/>
-      <c r="D81" s="79"/>
-      <c r="E81" s="79"/>
-      <c r="F81" s="79"/>
-      <c r="G81" s="79"/>
-      <c r="H81" s="179">
-        <f>-(H72)</f>
-        <v>-2438542.4499999997</v>
-      </c>
-    </row>
-    <row r="82" spans="1:11">
-      <c r="A82" s="78" t="s">
-        <v>84</v>
-      </c>
-      <c r="B82" s="79"/>
-      <c r="C82" s="79"/>
-      <c r="D82" s="79"/>
-      <c r="E82" s="79"/>
-      <c r="F82" s="79"/>
-      <c r="G82" s="79"/>
-      <c r="H82" s="179">
-        <f>-H59</f>
-        <v>-80000</v>
-      </c>
-      <c r="J82" s="186" t="s">
-        <v>151</v>
-      </c>
-      <c r="K82" s="6"/>
+        <v>2862785.4767692201</v>
+      </c>
     </row>
     <row r="83" spans="1:11">
       <c r="A83" s="78" t="s">
-        <v>144</v>
+        <v>153</v>
       </c>
       <c r="B83" s="79"/>
       <c r="C83" s="79"/>
@@ -3340,14 +3342,14 @@
       <c r="E83" s="79"/>
       <c r="F83" s="79"/>
       <c r="G83" s="79"/>
-      <c r="H83" s="121">
-        <v>133680</v>
-      </c>
-      <c r="J83" s="7"/>
+      <c r="H83" s="179">
+        <f>-(H74)</f>
+        <v>-2477720.36</v>
+      </c>
     </row>
     <row r="84" spans="1:11">
       <c r="A84" s="78" t="s">
-        <v>71</v>
+        <v>84</v>
       </c>
       <c r="B84" s="79"/>
       <c r="C84" s="79"/>
@@ -3355,187 +3357,218 @@
       <c r="E84" s="79"/>
       <c r="F84" s="79"/>
       <c r="G84" s="79"/>
-      <c r="H84" s="121">
-        <f>180000-H83</f>
-        <v>46320</v>
-      </c>
-      <c r="I84" s="142"/>
-      <c r="J84" s="7"/>
+      <c r="H84" s="179">
+        <f>-H61</f>
+        <v>-1097000</v>
+      </c>
+      <c r="K84" s="6"/>
     </row>
     <row r="85" spans="1:11">
-      <c r="A85" s="12" t="s">
+      <c r="A85" s="78" t="s">
+        <v>144</v>
+      </c>
+      <c r="B85" s="79"/>
+      <c r="C85" s="79"/>
+      <c r="D85" s="79"/>
+      <c r="E85" s="79"/>
+      <c r="F85" s="79"/>
+      <c r="G85" s="79"/>
+      <c r="H85" s="121">
+        <v>154000</v>
+      </c>
+      <c r="J85" s="7"/>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" s="78" t="s">
+        <v>71</v>
+      </c>
+      <c r="B86" s="79"/>
+      <c r="C86" s="79"/>
+      <c r="D86" s="79"/>
+      <c r="E86" s="79"/>
+      <c r="F86" s="79"/>
+      <c r="G86" s="79"/>
+      <c r="H86" s="121">
+        <v>63214</v>
+      </c>
+      <c r="I86" s="142"/>
+      <c r="J86" s="7"/>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" s="12" t="s">
         <v>117</v>
       </c>
-      <c r="B85" s="83"/>
-      <c r="C85" s="4"/>
-      <c r="D85" s="4"/>
-      <c r="E85" s="4"/>
-      <c r="F85" s="4"/>
-      <c r="G85" s="4"/>
-      <c r="H85" s="98"/>
-    </row>
-    <row r="86" spans="1:11" ht="18">
-      <c r="A86" s="22" t="s">
+      <c r="B87" s="83"/>
+      <c r="C87" s="4"/>
+      <c r="D87" s="4"/>
+      <c r="E87" s="4"/>
+      <c r="F87" s="4"/>
+      <c r="G87" s="4"/>
+      <c r="H87" s="98"/>
+    </row>
+    <row r="88" spans="1:11" ht="18.75">
+      <c r="A88" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="B86" s="23"/>
-      <c r="C86" s="23"/>
-      <c r="D86" s="23"/>
-      <c r="E86" s="23"/>
-      <c r="F86" s="23"/>
-      <c r="G86" s="23"/>
-      <c r="H86" s="84">
-        <f>SUM(H79:H85)</f>
-        <v>6048732.7764576916</v>
-      </c>
-    </row>
-    <row r="87" spans="1:11" ht="15" thickBot="1"/>
-    <row r="88" spans="1:11" ht="16.2" thickBot="1">
-      <c r="A88" s="188" t="s">
+      <c r="B88" s="23"/>
+      <c r="C88" s="23"/>
+      <c r="D88" s="23"/>
+      <c r="E88" s="23"/>
+      <c r="F88" s="23"/>
+      <c r="G88" s="23"/>
+      <c r="H88" s="84">
+        <f>SUM(H81:H87)</f>
+        <v>4229401.2367692199</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" ht="15.75" thickBot="1"/>
+    <row r="90" spans="1:11" ht="16.5" thickBot="1">
+      <c r="A90" s="187" t="s">
         <v>97</v>
       </c>
-      <c r="B88" s="189"/>
-      <c r="C88" s="189"/>
-      <c r="D88" s="189"/>
-      <c r="E88" s="189"/>
-      <c r="F88" s="189"/>
-      <c r="G88" s="189"/>
-      <c r="H88" s="190"/>
-    </row>
-    <row r="89" spans="1:11" ht="15.6">
-      <c r="A89" s="87" t="s">
+      <c r="B90" s="188"/>
+      <c r="C90" s="188"/>
+      <c r="D90" s="188"/>
+      <c r="E90" s="188"/>
+      <c r="F90" s="188"/>
+      <c r="G90" s="188"/>
+      <c r="H90" s="189"/>
+    </row>
+    <row r="91" spans="1:11" ht="15.75">
+      <c r="A91" s="87" t="s">
         <v>12</v>
       </c>
-      <c r="B89" s="87"/>
-      <c r="C89" s="87"/>
-      <c r="D89" s="87"/>
-      <c r="E89" s="87"/>
-      <c r="F89" s="87"/>
-      <c r="G89" s="87"/>
-      <c r="H89" s="88">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="1:11">
-      <c r="A90" s="61" t="s">
+      <c r="B91" s="87"/>
+      <c r="C91" s="87"/>
+      <c r="D91" s="87"/>
+      <c r="E91" s="87"/>
+      <c r="F91" s="87"/>
+      <c r="G91" s="87"/>
+      <c r="H91" s="88">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" s="61" t="s">
         <v>118</v>
       </c>
-      <c r="B90" s="91"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="61"/>
-      <c r="E90" s="61"/>
-      <c r="F90" s="61"/>
-      <c r="G90" s="61"/>
-      <c r="H90" s="125"/>
-    </row>
-    <row r="91" spans="1:11">
-      <c r="A91" s="61"/>
-      <c r="B91" s="97"/>
-      <c r="C91" s="61"/>
-      <c r="D91" s="61"/>
-      <c r="E91" s="61"/>
-      <c r="F91" s="61"/>
-      <c r="G91" s="61"/>
-      <c r="H91" s="21"/>
-    </row>
-    <row r="92" spans="1:11">
-      <c r="A92" s="61"/>
-      <c r="B92" s="61"/>
-      <c r="C92" s="61"/>
+      <c r="B92" s="91"/>
+      <c r="C92" s="4"/>
       <c r="D92" s="61"/>
       <c r="E92" s="61"/>
       <c r="F92" s="61"/>
       <c r="G92" s="61"/>
-      <c r="H92" s="21"/>
+      <c r="H92" s="125"/>
     </row>
     <row r="93" spans="1:11">
-      <c r="A93" s="85" t="s">
+      <c r="A93" s="61"/>
+      <c r="B93" s="97"/>
+      <c r="C93" s="61"/>
+      <c r="D93" s="61"/>
+      <c r="E93" s="61"/>
+      <c r="F93" s="61"/>
+      <c r="G93" s="61"/>
+      <c r="H93" s="21"/>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" s="61"/>
+      <c r="B94" s="61"/>
+      <c r="C94" s="61"/>
+      <c r="D94" s="61"/>
+      <c r="E94" s="61"/>
+      <c r="F94" s="61"/>
+      <c r="G94" s="61"/>
+      <c r="H94" s="21"/>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" s="85" t="s">
         <v>11</v>
       </c>
-      <c r="B93" s="85"/>
-      <c r="C93" s="85"/>
-      <c r="D93" s="85"/>
-      <c r="E93" s="85"/>
-      <c r="F93" s="85"/>
-      <c r="G93" s="85"/>
-      <c r="H93" s="86">
-        <f>SUM(H89:H92)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:11" hidden="1">
-      <c r="A96" s="187"/>
-      <c r="B96" s="187"/>
-      <c r="C96" s="187"/>
-      <c r="D96" s="187"/>
-      <c r="E96" s="187"/>
-      <c r="F96" s="187"/>
-      <c r="G96" s="187"/>
-      <c r="H96" s="187"/>
-    </row>
-    <row r="97" spans="1:8" hidden="1">
-      <c r="A97" s="187"/>
-      <c r="B97" s="187"/>
-      <c r="C97" s="187"/>
-      <c r="D97" s="187"/>
-      <c r="E97" s="187"/>
-      <c r="F97" s="187"/>
-      <c r="G97" s="187"/>
-      <c r="H97" s="187"/>
+      <c r="B95" s="85"/>
+      <c r="C95" s="85"/>
+      <c r="D95" s="85"/>
+      <c r="E95" s="85"/>
+      <c r="F95" s="85"/>
+      <c r="G95" s="85"/>
+      <c r="H95" s="86">
+        <f>SUM(H91:H94)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="98" spans="1:8" hidden="1">
-      <c r="A98" s="187"/>
-      <c r="B98" s="187"/>
-      <c r="C98" s="187"/>
-      <c r="D98" s="187"/>
-      <c r="E98" s="187"/>
-      <c r="F98" s="187"/>
-      <c r="G98" s="187"/>
-      <c r="H98" s="187"/>
+      <c r="A98" s="186"/>
+      <c r="B98" s="186"/>
+      <c r="C98" s="186"/>
+      <c r="D98" s="186"/>
+      <c r="E98" s="186"/>
+      <c r="F98" s="186"/>
+      <c r="G98" s="186"/>
+      <c r="H98" s="186"/>
     </row>
     <row r="99" spans="1:8" hidden="1">
-      <c r="A99" s="187"/>
-      <c r="B99" s="187"/>
-      <c r="C99" s="187"/>
-      <c r="D99" s="187"/>
-      <c r="E99" s="187"/>
-      <c r="F99" s="187"/>
-      <c r="G99" s="187"/>
-      <c r="H99" s="187"/>
+      <c r="A99" s="186"/>
+      <c r="B99" s="186"/>
+      <c r="C99" s="186"/>
+      <c r="D99" s="186"/>
+      <c r="E99" s="186"/>
+      <c r="F99" s="186"/>
+      <c r="G99" s="186"/>
+      <c r="H99" s="186"/>
+    </row>
+    <row r="100" spans="1:8" hidden="1">
+      <c r="A100" s="186"/>
+      <c r="B100" s="186"/>
+      <c r="C100" s="186"/>
+      <c r="D100" s="186"/>
+      <c r="E100" s="186"/>
+      <c r="F100" s="186"/>
+      <c r="G100" s="186"/>
+      <c r="H100" s="186"/>
+    </row>
+    <row r="101" spans="1:8" hidden="1">
+      <c r="A101" s="186"/>
+      <c r="B101" s="186"/>
+      <c r="C101" s="186"/>
+      <c r="D101" s="186"/>
+      <c r="E101" s="186"/>
+      <c r="F101" s="186"/>
+      <c r="G101" s="186"/>
+      <c r="H101" s="186"/>
     </row>
   </sheetData>
-  <mergeCells count="31">
-    <mergeCell ref="A41:G41"/>
-    <mergeCell ref="A49:H49"/>
-    <mergeCell ref="A67:G67"/>
-    <mergeCell ref="A59:G59"/>
-    <mergeCell ref="A66:G66"/>
-    <mergeCell ref="A62:G62"/>
-    <mergeCell ref="A60:H61"/>
+  <mergeCells count="32">
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="A62:H63"/>
+    <mergeCell ref="A55:G55"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="E3:H3"/>
-    <mergeCell ref="J70:K70"/>
-    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="J72:K72"/>
+    <mergeCell ref="A70:G70"/>
     <mergeCell ref="A23:H23"/>
     <mergeCell ref="A19:H19"/>
-    <mergeCell ref="A63:G63"/>
+    <mergeCell ref="A65:G65"/>
     <mergeCell ref="A12:H12"/>
-    <mergeCell ref="A52:H52"/>
-    <mergeCell ref="A55:H55"/>
+    <mergeCell ref="A53:H53"/>
+    <mergeCell ref="A57:H57"/>
     <mergeCell ref="A14:H14"/>
     <mergeCell ref="A32:H32"/>
     <mergeCell ref="A36:H36"/>
-    <mergeCell ref="A45:H45"/>
+    <mergeCell ref="A46:H46"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A96:H99"/>
-    <mergeCell ref="A88:H88"/>
-    <mergeCell ref="A78:H78"/>
-    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A98:H101"/>
+    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A80:H80"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A74:G74"/>
     <mergeCell ref="A73:G73"/>
     <mergeCell ref="A72:G72"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A70:G70"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
@@ -3546,24 +3579,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.5546875" customWidth="1"/>
-    <col min="2" max="2" width="9.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.88671875" customWidth="1"/>
-    <col min="4" max="4" width="7.88671875" customWidth="1"/>
+    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="2" max="2" width="9.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.85546875" customWidth="1"/>
+    <col min="4" max="4" width="7.85546875" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.33203125" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.33203125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.5546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.28515625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="2" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="11" width="10.5546875" style="2" customWidth="1"/>
-    <col min="12" max="12" width="13.6640625" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.5546875" customWidth="1"/>
-    <col min="14" max="14" width="13.44140625" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="15.109375" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.7109375" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.5703125" customWidth="1"/>
+    <col min="14" max="14" width="13.42578125" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="15.140625" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="26.25" customHeight="1">
@@ -3659,16 +3692,16 @@
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="120"/>
-      <c r="B5" s="230">
+      <c r="B5" s="232">
         <f>C2</f>
         <v>3283892.26</v>
       </c>
-      <c r="C5" s="230"/>
+      <c r="C5" s="232"/>
       <c r="D5" s="21"/>
-      <c r="E5" s="236">
-        <v>0</v>
-      </c>
-      <c r="F5" s="237"/>
+      <c r="E5" s="238">
+        <v>1097000</v>
+      </c>
+      <c r="F5" s="239"/>
       <c r="G5" s="114"/>
       <c r="H5" s="114"/>
       <c r="I5" s="114"/>
@@ -3681,13 +3714,13 @@
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="120"/>
-      <c r="B6" s="232"/>
-      <c r="C6" s="233"/>
+      <c r="B6" s="234"/>
+      <c r="C6" s="235"/>
       <c r="D6" s="21"/>
-      <c r="E6" s="232" t="s">
+      <c r="E6" s="234" t="s">
         <v>146</v>
       </c>
-      <c r="F6" s="233"/>
+      <c r="F6" s="235"/>
       <c r="G6" s="114"/>
       <c r="H6" s="114"/>
       <c r="I6" s="114"/>
@@ -3700,11 +3733,11 @@
     </row>
     <row r="7" spans="1:17" ht="18.75" customHeight="1">
       <c r="A7" s="120"/>
-      <c r="B7" s="230"/>
-      <c r="C7" s="230"/>
+      <c r="B7" s="232"/>
+      <c r="C7" s="232"/>
       <c r="D7" s="21"/>
-      <c r="E7" s="234"/>
-      <c r="F7" s="235"/>
+      <c r="E7" s="236"/>
+      <c r="F7" s="237"/>
       <c r="G7" s="114"/>
       <c r="H7" s="114"/>
       <c r="I7" s="114"/>
@@ -3779,26 +3812,27 @@
         <v>4.0500000000000001E-2</v>
       </c>
       <c r="F9" s="98">
-        <v>1172.4310599999444</v>
+        <v>146111.69953921993</v>
       </c>
       <c r="G9" s="176">
-        <v>0</v>
+        <f>F9</f>
+        <v>146111.69953921993</v>
       </c>
       <c r="H9" s="68">
         <f>IF(F9&gt;G9,F9-G9,0)</f>
-        <v>1172.4310599999444</v>
+        <v>0</v>
       </c>
       <c r="I9" s="68">
         <f>H9*3.7%</f>
-        <v>43.379949219997947</v>
+        <v>0</v>
       </c>
       <c r="J9" s="68">
         <f>IF(G9&gt;F9,G9-F9,0)</f>
         <v>0</v>
       </c>
       <c r="K9" s="68">
-        <f>F$4*E9</f>
-        <v>11898.252</v>
+        <f>E$5*E9</f>
+        <v>44428.5</v>
       </c>
       <c r="L9" s="68">
         <f>E$7*E9</f>
@@ -3814,7 +3848,7 @@
       </c>
       <c r="O9" s="183">
         <f>H9+I9-J9+K9+M9+N9+L9</f>
-        <v>146111.69953921993</v>
+        <v>177426.13652999999</v>
       </c>
     </row>
     <row r="10" spans="1:17" ht="15" customHeight="1">
@@ -3832,11 +3866,11 @@
         <v>6.4799999999999996E-2</v>
       </c>
       <c r="F10" s="17">
-        <v>167033.42164799996</v>
+        <v>231833.42164799996</v>
       </c>
       <c r="G10" s="176">
         <f>F10</f>
-        <v>167033.42164799996</v>
+        <v>231833.42164799996</v>
       </c>
       <c r="H10" s="24">
         <f t="shared" ref="H10:H31" si="0">IF(F10&gt;G10,F10-G10,0)</f>
@@ -3850,9 +3884,9 @@
         <f t="shared" ref="J10:J31" si="1">IF(G10&gt;F10,G10-F10,0)</f>
         <v>0</v>
       </c>
-      <c r="K10" s="24">
-        <f t="shared" ref="K10:K31" si="2">F$4*E10</f>
-        <v>19037.2032</v>
+      <c r="K10" s="68">
+        <f t="shared" ref="K10:K31" si="2">E$5*E10</f>
+        <v>71085.599999999991</v>
       </c>
       <c r="L10" s="68">
         <f t="shared" ref="L10:L31" si="3">E$7*E10</f>
@@ -3868,7 +3902,7 @@
       </c>
       <c r="O10" s="183">
         <f t="shared" ref="O10:O31" si="6">H10+I10-J10+K10+M10+N10+L10</f>
-        <v>231833.42164799996</v>
+        <v>283881.81844799995</v>
       </c>
     </row>
     <row r="11" spans="1:17" ht="15" customHeight="1">
@@ -3888,11 +3922,11 @@
         <v>4.82E-2</v>
       </c>
       <c r="F11" s="98">
-        <v>124243.995732</v>
+        <v>172443.99573199998</v>
       </c>
       <c r="G11" s="176">
         <f>F11</f>
-        <v>124243.995732</v>
+        <v>172443.99573199998</v>
       </c>
       <c r="H11" s="68">
         <f t="shared" si="0"/>
@@ -3908,7 +3942,7 @@
       </c>
       <c r="K11" s="68">
         <f t="shared" si="2"/>
-        <v>14160.388800000001</v>
+        <v>52875.4</v>
       </c>
       <c r="L11" s="68">
         <f t="shared" si="3"/>
@@ -3924,7 +3958,7 @@
       </c>
       <c r="O11" s="183">
         <f t="shared" si="6"/>
-        <v>172443.99573199998</v>
+        <v>211159.00693199999</v>
       </c>
       <c r="P11" s="171"/>
     </row>
@@ -3945,16 +3979,16 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F12" s="147">
-        <v>5143906.2370854998</v>
+        <v>5525636.4477676637</v>
       </c>
       <c r="G12" s="177"/>
       <c r="H12" s="148">
         <f t="shared" si="0"/>
-        <v>5143906.2370854998</v>
+        <v>5525636.4477676637</v>
       </c>
       <c r="I12" s="148">
         <f t="shared" si="7"/>
-        <v>190324.53077216353</v>
+        <v>204448.54856740357</v>
       </c>
       <c r="J12" s="148">
         <f t="shared" si="1"/>
@@ -3962,7 +3996,7 @@
       </c>
       <c r="K12" s="148">
         <f t="shared" si="2"/>
-        <v>15717.444</v>
+        <v>58689.5</v>
       </c>
       <c r="L12" s="148">
         <f t="shared" si="3"/>
@@ -3978,7 +4012,7 @@
       </c>
       <c r="O12" s="184">
         <f t="shared" si="6"/>
-        <v>5525636.4477676637</v>
+        <v>5964462.7322450671</v>
       </c>
     </row>
     <row r="13" spans="1:17" ht="15" customHeight="1">
@@ -3996,11 +4030,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F13" s="17">
-        <v>99240.536009999982</v>
+        <v>137740.53600999998</v>
       </c>
       <c r="G13" s="176">
         <f>F13</f>
-        <v>99240.536009999982</v>
+        <v>137740.53600999998</v>
       </c>
       <c r="H13" s="24">
         <f t="shared" si="0"/>
@@ -4014,9 +4048,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K13" s="24">
+      <c r="K13" s="68">
         <f t="shared" si="2"/>
-        <v>11310.683999999999</v>
+        <v>42234.5</v>
       </c>
       <c r="L13" s="68">
         <f t="shared" si="3"/>
@@ -4032,7 +4066,7 @@
       </c>
       <c r="O13" s="183">
         <f t="shared" si="6"/>
-        <v>137740.53600999998</v>
+        <v>168664.35200999997</v>
       </c>
     </row>
     <row r="14" spans="1:17" ht="15" customHeight="1">
@@ -4050,11 +4084,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F14" s="17">
-        <v>92523.216667999979</v>
+        <v>128438.57773399999</v>
       </c>
       <c r="G14" s="176">
         <f>F14</f>
-        <v>92523.216667999979</v>
+        <v>128438.57773399999</v>
       </c>
       <c r="H14" s="24">
         <f t="shared" si="0"/>
@@ -4068,9 +4102,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K14" s="24">
+      <c r="K14" s="68">
         <f t="shared" si="2"/>
-        <v>10546.845600000001</v>
+        <v>39382.300000000003</v>
       </c>
       <c r="L14" s="68">
         <f t="shared" si="3"/>
@@ -4086,7 +4120,7 @@
       </c>
       <c r="O14" s="183">
         <f t="shared" si="6"/>
-        <v>128438.57773399999</v>
+        <v>157274.03213399998</v>
       </c>
     </row>
     <row r="15" spans="1:17" ht="15" customHeight="1">
@@ -4106,11 +4140,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F15" s="17">
-        <v>106715.79716399999</v>
+        <v>148115.79716399999</v>
       </c>
       <c r="G15" s="176">
         <f>F15</f>
-        <v>106715.79716399999</v>
+        <v>148115.79716399999</v>
       </c>
       <c r="H15" s="24">
         <f t="shared" si="0"/>
@@ -4124,9 +4158,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K15" s="24">
+      <c r="K15" s="68">
         <f t="shared" si="2"/>
-        <v>12162.6576</v>
+        <v>45415.799999999996</v>
       </c>
       <c r="L15" s="68">
         <f t="shared" si="3"/>
@@ -4141,7 +4175,7 @@
       </c>
       <c r="O15" s="183">
         <f t="shared" si="6"/>
-        <v>148115.79716399999</v>
+        <v>181368.93956399997</v>
       </c>
       <c r="Q15" s="180"/>
     </row>
@@ -4162,11 +4196,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F16" s="17">
-        <v>137905.67990999998</v>
+        <v>191405.67990999998</v>
       </c>
       <c r="G16" s="176">
         <f>F16</f>
-        <v>137905.67990999998</v>
+        <v>191405.67990999998</v>
       </c>
       <c r="H16" s="24">
         <f t="shared" si="0"/>
@@ -4180,9 +4214,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K16" s="24">
+      <c r="K16" s="68">
         <f t="shared" si="2"/>
-        <v>15717.444</v>
+        <v>58689.5</v>
       </c>
       <c r="L16" s="68">
         <f t="shared" si="3"/>
@@ -4198,7 +4232,7 @@
       </c>
       <c r="O16" s="183">
         <f t="shared" si="6"/>
-        <v>191405.67990999998</v>
+        <v>234377.73590999999</v>
       </c>
       <c r="Q16" s="180"/>
     </row>
@@ -4219,24 +4253,24 @@
         <v>3.85E-2</v>
       </c>
       <c r="F17" s="17">
-        <v>99240.536009999982</v>
+        <v>240652.97185236996</v>
       </c>
       <c r="G17" s="176"/>
       <c r="H17" s="24">
         <f t="shared" si="0"/>
-        <v>99240.536009999982</v>
+        <v>240652.97185236996</v>
       </c>
       <c r="I17" s="24">
         <f t="shared" si="7"/>
-        <v>3671.8998323699998</v>
+        <v>8904.1599585376898</v>
       </c>
       <c r="J17" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K17" s="24">
+      <c r="K17" s="68">
         <f t="shared" si="2"/>
-        <v>11310.683999999999</v>
+        <v>42234.5</v>
       </c>
       <c r="L17" s="68">
         <f t="shared" si="3"/>
@@ -4252,7 +4286,7 @@
       </c>
       <c r="O17" s="183">
         <f t="shared" si="6"/>
-        <v>240652.97185236996</v>
+        <v>418221.4838209076</v>
       </c>
       <c r="Q17" s="180"/>
     </row>
@@ -4271,11 +4305,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F18" s="98">
-        <v>77881.52363491038</v>
+        <v>23120.101368910371</v>
       </c>
       <c r="G18" s="176">
-        <f>25000+RESUMEN!H42+RESUMEN!H37</f>
-        <v>193200</v>
+        <f>RESUMEN!H37+RESUMEN!H43+RESUMEN!H48</f>
+        <v>213200</v>
       </c>
       <c r="H18" s="68">
         <f>IF(F18&gt;G18,F18-G18,0)</f>
@@ -4287,11 +4321,11 @@
       </c>
       <c r="J18" s="68">
         <f t="shared" si="1"/>
-        <v>115318.47636508962</v>
+        <v>190079.89863108963</v>
       </c>
       <c r="K18" s="68">
         <f t="shared" si="2"/>
-        <v>10546.845600000001</v>
+        <v>39382.300000000003</v>
       </c>
       <c r="L18" s="68">
         <f t="shared" si="3"/>
@@ -4307,7 +4341,7 @@
       </c>
       <c r="O18" s="183">
         <f t="shared" si="6"/>
-        <v>13120.101368910371</v>
+        <v>-32805.866497089621</v>
       </c>
       <c r="Q18" s="180"/>
     </row>
@@ -4328,16 +4362,16 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F19" s="147">
-        <v>3630635.9079769286</v>
+        <v>3913085.233736075</v>
       </c>
       <c r="G19" s="177"/>
       <c r="H19" s="148">
         <f t="shared" si="0"/>
-        <v>3630635.9079769286</v>
+        <v>3913085.233736075</v>
       </c>
       <c r="I19" s="148">
         <f t="shared" si="7"/>
-        <v>134333.52859514637</v>
+        <v>144784.15364823479</v>
       </c>
       <c r="J19" s="148">
         <f t="shared" si="1"/>
@@ -4345,7 +4379,7 @@
       </c>
       <c r="K19" s="148">
         <f t="shared" si="2"/>
-        <v>12162.6576</v>
+        <v>45415.799999999996</v>
       </c>
       <c r="L19" s="148">
         <f t="shared" si="3"/>
@@ -4361,7 +4395,7 @@
       </c>
       <c r="O19" s="184">
         <f t="shared" si="6"/>
-        <v>3913085.233736075</v>
+        <v>4239238.3269483093</v>
       </c>
       <c r="Q19" s="180"/>
     </row>
@@ -4382,11 +4416,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F20" s="17">
-        <v>137905.67990999998</v>
+        <v>191405.67990999998</v>
       </c>
       <c r="G20" s="176">
         <f>F20</f>
-        <v>137905.67990999998</v>
+        <v>191405.67990999998</v>
       </c>
       <c r="H20" s="24">
         <f t="shared" si="0"/>
@@ -4400,9 +4434,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K20" s="24">
+      <c r="K20" s="68">
         <f t="shared" si="2"/>
-        <v>15717.444</v>
+        <v>58689.5</v>
       </c>
       <c r="L20" s="68">
         <f t="shared" si="3"/>
@@ -4418,7 +4452,7 @@
       </c>
       <c r="O20" s="183">
         <f t="shared" si="6"/>
-        <v>191405.67990999998</v>
+        <v>234377.73590999999</v>
       </c>
       <c r="Q20" s="180"/>
     </row>
@@ -4437,18 +4471,18 @@
         <v>3.85E-2</v>
       </c>
       <c r="F21" s="147">
-        <v>1562548.2616261418</v>
+        <v>1758103.0833163089</v>
       </c>
       <c r="G21" s="178">
         <v>0</v>
       </c>
       <c r="H21" s="148">
         <f t="shared" si="0"/>
-        <v>1562548.2616261418</v>
+        <v>1758103.0833163089</v>
       </c>
       <c r="I21" s="148">
         <f t="shared" si="7"/>
-        <v>57814.285680167253</v>
+        <v>65049.814082703437</v>
       </c>
       <c r="J21" s="148">
         <f t="shared" si="1"/>
@@ -4456,7 +4490,7 @@
       </c>
       <c r="K21" s="148">
         <f t="shared" si="2"/>
-        <v>11310.683999999999</v>
+        <v>42234.5</v>
       </c>
       <c r="L21" s="148">
         <f t="shared" si="3"/>
@@ -4472,7 +4506,7 @@
       </c>
       <c r="O21" s="184">
         <f t="shared" si="6"/>
-        <v>1758103.0833163089</v>
+        <v>1991817.2494090125</v>
       </c>
       <c r="Q21" s="180"/>
     </row>
@@ -4493,11 +4527,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F22" s="17">
-        <v>92538.577733999991</v>
+        <v>128438.57773399999</v>
       </c>
       <c r="G22" s="176">
         <f>F22</f>
-        <v>92538.577733999991</v>
+        <v>128438.57773399999</v>
       </c>
       <c r="H22" s="24">
         <f t="shared" si="0"/>
@@ -4511,9 +4545,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K22" s="24">
+      <c r="K22" s="68">
         <f t="shared" si="2"/>
-        <v>10546.845600000001</v>
+        <v>39382.300000000003</v>
       </c>
       <c r="L22" s="68">
         <f t="shared" si="3"/>
@@ -4529,7 +4563,7 @@
       </c>
       <c r="O22" s="183">
         <f t="shared" si="6"/>
-        <v>128438.57773399999</v>
+        <v>157274.03213399998</v>
       </c>
       <c r="Q22" s="180"/>
     </row>
@@ -4550,11 +4584,11 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F23" s="17">
-        <v>106715.79716399999</v>
+        <v>148115.79716399999</v>
       </c>
       <c r="G23" s="176">
-        <f>F23</f>
-        <v>106715.79716399999</v>
+        <f>135953+12163</f>
+        <v>148116</v>
       </c>
       <c r="H23" s="24">
         <f t="shared" si="0"/>
@@ -4566,11 +4600,11 @@
       </c>
       <c r="J23" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K23" s="24">
+        <v>0.20283600001130253</v>
+      </c>
+      <c r="K23" s="68">
         <f t="shared" si="2"/>
-        <v>12162.6576</v>
+        <v>45415.799999999996</v>
       </c>
       <c r="L23" s="68">
         <f t="shared" si="3"/>
@@ -4586,7 +4620,7 @@
       </c>
       <c r="O23" s="183">
         <f t="shared" si="6"/>
-        <v>148115.79716399999</v>
+        <v>181368.73672799996</v>
       </c>
       <c r="Q23" s="180"/>
     </row>
@@ -4605,11 +4639,11 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F24" s="17">
-        <v>137905.67990999998</v>
+        <v>191405.67990999998</v>
       </c>
       <c r="G24" s="176">
         <f>F24</f>
-        <v>137905.67990999998</v>
+        <v>191405.67990999998</v>
       </c>
       <c r="H24" s="24">
         <f t="shared" si="0"/>
@@ -4623,9 +4657,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K24" s="24">
+      <c r="K24" s="68">
         <f t="shared" si="2"/>
-        <v>15717.444</v>
+        <v>58689.5</v>
       </c>
       <c r="L24" s="68">
         <f t="shared" si="3"/>
@@ -4641,7 +4675,7 @@
       </c>
       <c r="O24" s="183">
         <f t="shared" si="6"/>
-        <v>191405.67990999998</v>
+        <v>234377.73590999999</v>
       </c>
       <c r="Q24" s="180"/>
     </row>
@@ -4662,11 +4696,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F25" s="17">
-        <v>99240.536009999982</v>
+        <v>137740.53600999998</v>
       </c>
       <c r="G25" s="176">
-        <f>F25</f>
-        <v>99240.536009999982</v>
+        <f>126430+11311</f>
+        <v>137741</v>
       </c>
       <c r="H25" s="24">
         <f t="shared" si="0"/>
@@ -4678,11 +4712,11 @@
       </c>
       <c r="J25" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K25" s="24">
+        <v>0.46399000001838431</v>
+      </c>
+      <c r="K25" s="68">
         <f t="shared" si="2"/>
-        <v>11310.683999999999</v>
+        <v>42234.5</v>
       </c>
       <c r="L25" s="68">
         <f t="shared" si="3"/>
@@ -4698,7 +4732,7 @@
       </c>
       <c r="O25" s="183">
         <f t="shared" si="6"/>
-        <v>137740.53600999998</v>
+        <v>168663.88801999995</v>
       </c>
       <c r="Q25" s="181"/>
     </row>
@@ -4717,11 +4751,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F26" s="17">
-        <v>92538.577733999991</v>
+        <v>128438.57773399999</v>
       </c>
       <c r="G26" s="176">
         <f>F26</f>
-        <v>92538.577733999991</v>
+        <v>128438.57773399999</v>
       </c>
       <c r="H26" s="24">
         <f t="shared" si="0"/>
@@ -4735,9 +4769,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K26" s="24">
+      <c r="K26" s="68">
         <f t="shared" si="2"/>
-        <v>10546.845600000001</v>
+        <v>39382.300000000003</v>
       </c>
       <c r="L26" s="68">
         <f t="shared" si="3"/>
@@ -4753,7 +4787,7 @@
       </c>
       <c r="O26" s="183">
         <f t="shared" si="6"/>
-        <v>128438.57773399999</v>
+        <v>157274.03213399998</v>
       </c>
       <c r="Q26" s="180"/>
     </row>
@@ -4774,18 +4808,18 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F27" s="147">
-        <v>3401206.8652831158</v>
+        <v>3564415.7164625912</v>
       </c>
       <c r="G27" s="177">
-        <v>106800</v>
+        <v>148116.14000000001</v>
       </c>
       <c r="H27" s="170">
         <f t="shared" si="0"/>
-        <v>3294406.8652831158</v>
+        <v>3416299.5764625911</v>
       </c>
       <c r="I27" s="148">
         <f t="shared" si="7"/>
-        <v>121893.0540154753</v>
+        <v>126403.08432911588</v>
       </c>
       <c r="J27" s="148">
         <f t="shared" si="1"/>
@@ -4793,7 +4827,7 @@
       </c>
       <c r="K27" s="148">
         <f t="shared" si="2"/>
-        <v>12162.6576</v>
+        <v>45415.799999999996</v>
       </c>
       <c r="L27" s="148">
         <f t="shared" si="3"/>
@@ -4809,7 +4843,7 @@
       </c>
       <c r="O27" s="184">
         <f t="shared" si="6"/>
-        <v>3564415.7164625912</v>
+        <v>3724071.6003557066</v>
       </c>
       <c r="P27" s="182">
         <f>M27+N27</f>
@@ -4831,22 +4865,25 @@
         <v>5.3499999999999999E-2</v>
       </c>
       <c r="F28" s="17">
-        <v>2763998.3428144502</v>
+        <v>3041954.5174085847</v>
       </c>
       <c r="G28" s="176"/>
       <c r="H28" s="68">
         <f t="shared" si="0"/>
-        <v>2763998.3428144502</v>
+        <v>3041954.5174085847</v>
       </c>
       <c r="I28" s="24">
         <f t="shared" si="7"/>
-        <v>102267.93868413467</v>
+        <v>112552.31714411765</v>
       </c>
       <c r="J28" s="24">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K28" s="24"/>
+      <c r="K28" s="68">
+        <f t="shared" si="2"/>
+        <v>58689.5</v>
+      </c>
       <c r="L28" s="68">
         <f t="shared" si="3"/>
         <v>0</v>
@@ -4861,7 +4898,7 @@
       </c>
       <c r="O28" s="183">
         <f t="shared" si="6"/>
-        <v>3041954.5174085847</v>
+        <v>3388884.5704627023</v>
       </c>
       <c r="P28" s="7"/>
     </row>
@@ -4880,11 +4917,11 @@
         <v>3.85E-2</v>
       </c>
       <c r="F29" s="17">
-        <v>99240.536009999982</v>
+        <v>137740.53600999998</v>
       </c>
       <c r="G29" s="176">
         <f>F29</f>
-        <v>99240.536009999982</v>
+        <v>137740.53600999998</v>
       </c>
       <c r="H29" s="24">
         <f t="shared" si="0"/>
@@ -4898,9 +4935,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K29" s="24">
+      <c r="K29" s="68">
         <f t="shared" si="2"/>
-        <v>11310.683999999999</v>
+        <v>42234.5</v>
       </c>
       <c r="L29" s="68">
         <f t="shared" si="3"/>
@@ -4916,7 +4953,7 @@
       </c>
       <c r="O29" s="183">
         <f t="shared" si="6"/>
-        <v>137740.53600999998</v>
+        <v>168664.35200999997</v>
       </c>
       <c r="P29" s="7">
         <f>M29/2</f>
@@ -4947,11 +4984,11 @@
         <v>3.5900000000000001E-2</v>
       </c>
       <c r="F30" s="17">
-        <v>92538.577733999991</v>
+        <v>128438.57773399999</v>
       </c>
       <c r="G30" s="176">
         <f>F30</f>
-        <v>92538.577733999991</v>
+        <v>128438.57773399999</v>
       </c>
       <c r="H30" s="24">
         <f t="shared" si="0"/>
@@ -4965,9 +5002,9 @@
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="K30" s="24">
+      <c r="K30" s="68">
         <f t="shared" si="2"/>
-        <v>10546.845600000001</v>
+        <v>39382.300000000003</v>
       </c>
       <c r="L30" s="68">
         <f t="shared" si="3"/>
@@ -4983,7 +5020,7 @@
       </c>
       <c r="O30" s="183">
         <f t="shared" si="6"/>
-        <v>128438.57773399999</v>
+        <v>157274.03213399998</v>
       </c>
     </row>
     <row r="31" spans="1:18" ht="15" customHeight="1">
@@ -5001,11 +5038,10 @@
         <v>4.1399999999999999E-2</v>
       </c>
       <c r="F31" s="17">
-        <v>106715.79716399999</v>
+        <v>148115.79716399999</v>
       </c>
       <c r="G31" s="176">
-        <f>F31</f>
-        <v>106715.79716399999</v>
+        <v>153655</v>
       </c>
       <c r="H31" s="24">
         <f t="shared" si="0"/>
@@ -5017,11 +5053,11 @@
       </c>
       <c r="J31" s="24">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="K31" s="24">
+        <v>5539.2028360000113</v>
+      </c>
+      <c r="K31" s="68">
         <f t="shared" si="2"/>
-        <v>12162.6576</v>
+        <v>45415.799999999996</v>
       </c>
       <c r="L31" s="68">
         <f t="shared" si="3"/>
@@ -5037,10 +5073,10 @@
       </c>
       <c r="O31" s="183">
         <f t="shared" si="6"/>
-        <v>148115.79716399999</v>
-      </c>
-    </row>
-    <row r="32" spans="1:18" ht="15.6">
+        <v>175829.73672799996</v>
+      </c>
+    </row>
+    <row r="32" spans="1:18" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -5054,27 +5090,27 @@
       </c>
       <c r="F32" s="99">
         <f>SUM(F9:F31)</f>
-        <v>18373592.511993047</v>
+        <v>20562897.539019726</v>
       </c>
       <c r="G32" s="99">
-        <f>SUM(G9:G31)-428650</f>
-        <v>1564352.4065020001</v>
+        <f>SUM(G9:G31)</f>
+        <v>2862785.4767692201</v>
       </c>
       <c r="H32" s="122">
         <f>SUM(H9:H31)</f>
-        <v>16495908.581856135</v>
+        <v>17895731.830543593</v>
       </c>
       <c r="I32" s="54">
         <f>SUM(I9:I31)</f>
-        <v>610348.6175286771</v>
+        <v>662142.07773011306</v>
       </c>
       <c r="J32" s="99">
         <f t="shared" ref="J32" si="8">SUM(J9:J31)</f>
-        <v>115318.47636508962</v>
+        <v>195619.76829308967</v>
       </c>
       <c r="K32" s="90">
         <f>SUM(K9:K31)</f>
-        <v>278066.55600000004</v>
+        <v>1097000.0000000002</v>
       </c>
       <c r="L32" s="90"/>
       <c r="M32" s="54">
@@ -5087,124 +5123,124 @@
       </c>
       <c r="O32" s="54">
         <f>SUM(O9:O31)</f>
-        <v>20552897.539019726</v>
+        <v>22743146.39998062</v>
       </c>
     </row>
     <row r="33" spans="1:15" ht="14.25" customHeight="1"/>
     <row r="34" spans="1:15" hidden="1">
-      <c r="B34" s="229"/>
-      <c r="C34" s="229"/>
-      <c r="D34" s="229"/>
-      <c r="E34" s="229"/>
-      <c r="F34" s="229"/>
-      <c r="G34" s="229"/>
-      <c r="H34" s="229"/>
-      <c r="I34" s="229"/>
-      <c r="J34" s="229"/>
-      <c r="K34" s="229"/>
-      <c r="L34" s="229"/>
-      <c r="M34" s="229"/>
-      <c r="N34" s="229"/>
-      <c r="O34" s="229"/>
+      <c r="B34" s="231"/>
+      <c r="C34" s="231"/>
+      <c r="D34" s="231"/>
+      <c r="E34" s="231"/>
+      <c r="F34" s="231"/>
+      <c r="G34" s="231"/>
+      <c r="H34" s="231"/>
+      <c r="I34" s="231"/>
+      <c r="J34" s="231"/>
+      <c r="K34" s="231"/>
+      <c r="L34" s="231"/>
+      <c r="M34" s="231"/>
+      <c r="N34" s="231"/>
+      <c r="O34" s="231"/>
     </row>
     <row r="35" spans="1:15" hidden="1">
-      <c r="B35" s="229"/>
-      <c r="C35" s="229"/>
-      <c r="D35" s="229"/>
-      <c r="E35" s="229"/>
-      <c r="F35" s="229"/>
-      <c r="G35" s="229"/>
-      <c r="H35" s="229"/>
-      <c r="I35" s="229"/>
-      <c r="J35" s="229"/>
-      <c r="K35" s="229"/>
-      <c r="L35" s="229"/>
-      <c r="M35" s="229"/>
-      <c r="N35" s="229"/>
-      <c r="O35" s="229"/>
+      <c r="B35" s="231"/>
+      <c r="C35" s="231"/>
+      <c r="D35" s="231"/>
+      <c r="E35" s="231"/>
+      <c r="F35" s="231"/>
+      <c r="G35" s="231"/>
+      <c r="H35" s="231"/>
+      <c r="I35" s="231"/>
+      <c r="J35" s="231"/>
+      <c r="K35" s="231"/>
+      <c r="L35" s="231"/>
+      <c r="M35" s="231"/>
+      <c r="N35" s="231"/>
+      <c r="O35" s="231"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
-      <c r="B36" s="229"/>
-      <c r="C36" s="229"/>
-      <c r="D36" s="229"/>
-      <c r="E36" s="229"/>
-      <c r="F36" s="229"/>
-      <c r="G36" s="229"/>
-      <c r="H36" s="229"/>
-      <c r="I36" s="229"/>
-      <c r="J36" s="229"/>
-      <c r="K36" s="229"/>
-      <c r="L36" s="229"/>
-      <c r="M36" s="229"/>
-      <c r="N36" s="229"/>
-      <c r="O36" s="229"/>
+      <c r="B36" s="231"/>
+      <c r="C36" s="231"/>
+      <c r="D36" s="231"/>
+      <c r="E36" s="231"/>
+      <c r="F36" s="231"/>
+      <c r="G36" s="231"/>
+      <c r="H36" s="231"/>
+      <c r="I36" s="231"/>
+      <c r="J36" s="231"/>
+      <c r="K36" s="231"/>
+      <c r="L36" s="231"/>
+      <c r="M36" s="231"/>
+      <c r="N36" s="231"/>
+      <c r="O36" s="231"/>
     </row>
     <row r="37" spans="1:15" hidden="1">
-      <c r="B37" s="229"/>
-      <c r="C37" s="229"/>
-      <c r="D37" s="229"/>
-      <c r="E37" s="229"/>
-      <c r="F37" s="229"/>
-      <c r="G37" s="229"/>
-      <c r="H37" s="229"/>
-      <c r="I37" s="229"/>
-      <c r="J37" s="229"/>
-      <c r="K37" s="229"/>
-      <c r="L37" s="229"/>
-      <c r="M37" s="229"/>
-      <c r="N37" s="229"/>
-      <c r="O37" s="229"/>
+      <c r="B37" s="231"/>
+      <c r="C37" s="231"/>
+      <c r="D37" s="231"/>
+      <c r="E37" s="231"/>
+      <c r="F37" s="231"/>
+      <c r="G37" s="231"/>
+      <c r="H37" s="231"/>
+      <c r="I37" s="231"/>
+      <c r="J37" s="231"/>
+      <c r="K37" s="231"/>
+      <c r="L37" s="231"/>
+      <c r="M37" s="231"/>
+      <c r="N37" s="231"/>
+      <c r="O37" s="231"/>
     </row>
     <row r="38" spans="1:15" hidden="1">
-      <c r="A38" s="231"/>
-      <c r="B38" s="231"/>
-      <c r="C38" s="231"/>
-      <c r="D38" s="231"/>
-      <c r="E38" s="231"/>
-      <c r="F38" s="231"/>
-      <c r="G38" s="231"/>
-      <c r="H38" s="231"/>
-      <c r="I38" s="231"/>
-      <c r="J38" s="231"/>
-      <c r="K38" s="231"/>
-      <c r="L38" s="231"/>
-      <c r="M38" s="231"/>
-      <c r="N38" s="231"/>
-      <c r="O38" s="231"/>
+      <c r="A38" s="233"/>
+      <c r="B38" s="233"/>
+      <c r="C38" s="233"/>
+      <c r="D38" s="233"/>
+      <c r="E38" s="233"/>
+      <c r="F38" s="233"/>
+      <c r="G38" s="233"/>
+      <c r="H38" s="233"/>
+      <c r="I38" s="233"/>
+      <c r="J38" s="233"/>
+      <c r="K38" s="233"/>
+      <c r="L38" s="233"/>
+      <c r="M38" s="233"/>
+      <c r="N38" s="233"/>
+      <c r="O38" s="233"/>
     </row>
     <row r="39" spans="1:15" hidden="1">
-      <c r="A39" s="231"/>
-      <c r="B39" s="231"/>
-      <c r="C39" s="231"/>
-      <c r="D39" s="231"/>
-      <c r="E39" s="231"/>
-      <c r="F39" s="231"/>
-      <c r="G39" s="231"/>
-      <c r="H39" s="231"/>
-      <c r="I39" s="231"/>
-      <c r="J39" s="231"/>
-      <c r="K39" s="231"/>
-      <c r="L39" s="231"/>
-      <c r="M39" s="231"/>
-      <c r="N39" s="231"/>
-      <c r="O39" s="231"/>
+      <c r="A39" s="233"/>
+      <c r="B39" s="233"/>
+      <c r="C39" s="233"/>
+      <c r="D39" s="233"/>
+      <c r="E39" s="233"/>
+      <c r="F39" s="233"/>
+      <c r="G39" s="233"/>
+      <c r="H39" s="233"/>
+      <c r="I39" s="233"/>
+      <c r="J39" s="233"/>
+      <c r="K39" s="233"/>
+      <c r="L39" s="233"/>
+      <c r="M39" s="233"/>
+      <c r="N39" s="233"/>
+      <c r="O39" s="233"/>
     </row>
     <row r="40" spans="1:15" hidden="1">
-      <c r="A40" s="231"/>
-      <c r="B40" s="231"/>
-      <c r="C40" s="231"/>
-      <c r="D40" s="231"/>
-      <c r="E40" s="231"/>
-      <c r="F40" s="231"/>
-      <c r="G40" s="231"/>
-      <c r="H40" s="231"/>
-      <c r="I40" s="231"/>
-      <c r="J40" s="231"/>
-      <c r="K40" s="231"/>
-      <c r="L40" s="231"/>
-      <c r="M40" s="231"/>
-      <c r="N40" s="231"/>
-      <c r="O40" s="231"/>
+      <c r="A40" s="233"/>
+      <c r="B40" s="233"/>
+      <c r="C40" s="233"/>
+      <c r="D40" s="233"/>
+      <c r="E40" s="233"/>
+      <c r="F40" s="233"/>
+      <c r="G40" s="233"/>
+      <c r="H40" s="233"/>
+      <c r="I40" s="233"/>
+      <c r="J40" s="233"/>
+      <c r="K40" s="233"/>
+      <c r="L40" s="233"/>
+      <c r="M40" s="233"/>
+      <c r="N40" s="233"/>
+      <c r="O40" s="233"/>
     </row>
     <row r="41" spans="1:15">
       <c r="O41" s="7"/>
@@ -5229,25 +5265,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="4.109375" customWidth="1"/>
-    <col min="3" max="3" width="19.33203125" customWidth="1"/>
+    <col min="1" max="1" width="4.140625" customWidth="1"/>
+    <col min="3" max="3" width="19.28515625" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.33203125" customWidth="1"/>
-    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.28515625" customWidth="1"/>
+    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="238" t="s">
+      <c r="A1" s="240" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="239"/>
-      <c r="C1" s="239"/>
-      <c r="D1" s="239"/>
-      <c r="E1" s="239"/>
-      <c r="F1" s="239"/>
-      <c r="G1" s="240"/>
+      <c r="B1" s="241"/>
+      <c r="C1" s="241"/>
+      <c r="D1" s="241"/>
+      <c r="E1" s="241"/>
+      <c r="F1" s="241"/>
+      <c r="G1" s="242"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="30"/>
@@ -5283,13 +5319,13 @@
       <c r="C6" s="16"/>
       <c r="G6" s="31"/>
     </row>
-    <row r="7" spans="1:7" ht="15" thickBot="1">
+    <row r="7" spans="1:7" ht="15.75" thickBot="1">
       <c r="A7" s="62"/>
       <c r="B7" s="32"/>
       <c r="C7" s="16"/>
       <c r="G7" s="31"/>
     </row>
-    <row r="8" spans="1:7" ht="29.4" thickBot="1">
+    <row r="8" spans="1:7" ht="30.75" thickBot="1">
       <c r="A8" s="26" t="s">
         <v>0</v>
       </c>
@@ -5650,7 +5686,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.6">
+    <row r="24" spans="1:7" ht="15.75">
       <c r="A24" s="51">
         <v>16</v>
       </c>
@@ -5672,7 +5708,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.6">
+    <row r="25" spans="1:7" ht="15.75">
       <c r="A25" s="51">
         <v>17</v>
       </c>
@@ -5694,7 +5730,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.6">
+    <row r="26" spans="1:7" ht="15.75">
       <c r="A26" s="51">
         <v>18</v>
       </c>
@@ -5716,7 +5752,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.6">
+    <row r="27" spans="1:7" ht="15.75">
       <c r="A27" s="51">
         <v>19</v>
       </c>
@@ -5742,7 +5778,7 @@
         <v>17603.28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.6">
+    <row r="28" spans="1:7" ht="15.75">
       <c r="A28" s="51">
         <v>20</v>
       </c>
@@ -5764,7 +5800,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.6">
+    <row r="29" spans="1:7" ht="15.75">
       <c r="A29" s="51">
         <v>21</v>
       </c>
@@ -5786,7 +5822,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.6">
+    <row r="30" spans="1:7" ht="15.75">
       <c r="A30" s="51">
         <v>22</v>
       </c>
@@ -5808,7 +5844,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.6">
+    <row r="31" spans="1:7" ht="15.75">
       <c r="A31" s="51">
         <v>23</v>
       </c>
@@ -5830,7 +5866,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.6">
+    <row r="32" spans="1:7" ht="15.75">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>

--- a/2026/BRIN 3219/Junio/BRIN3219-EXPENSAS-Junio.xlsx
+++ b/2026/BRIN 3219/Junio/BRIN3219-EXPENSAS-Junio.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 3219\Junio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BRIN 3219\Junio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A5C7752-547C-461D-B1D0-A21D596A641E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36F61793-5F1A-485E-94E6-F84FFC13CC6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="27" r:id="rId1"/>
@@ -25,9 +25,6 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -1638,9 +1635,103 @@
     <xf numFmtId="44" fontId="2" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="44" fontId="2" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="31" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="7" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1659,12 +1750,6 @@
     <xf numFmtId="0" fontId="24" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="3" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1686,93 +1771,6 @@
     <xf numFmtId="0" fontId="24" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="22" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="1" fontId="23" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1809,7 +1807,6 @@
     <xf numFmtId="0" fontId="3" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hipervínculo" xfId="2" builtinId="8"/>
@@ -2257,16 +2254,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:K101"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="28.7109375" customWidth="1"/>
-    <col min="2" max="2" width="11.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.42578125" customWidth="1"/>
-    <col min="6" max="6" width="15.7109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="25.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.7109375" customWidth="1"/>
-    <col min="9" max="9" width="13.5703125" customWidth="1"/>
-    <col min="10" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="28.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.44140625" customWidth="1"/>
+    <col min="6" max="6" width="15.6640625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="25.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="19.6640625" customWidth="1"/>
+    <col min="9" max="9" width="13.5546875" customWidth="1"/>
+    <col min="10" max="10" width="13.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
@@ -2281,23 +2278,23 @@
     </row>
     <row r="2" spans="1:9" ht="48" customHeight="1">
       <c r="A2" s="10"/>
-      <c r="D2" s="202"/>
-      <c r="E2" s="203"/>
-      <c r="F2" s="203"/>
-      <c r="G2" s="203"/>
-      <c r="H2" s="204"/>
+      <c r="D2" s="206"/>
+      <c r="E2" s="207"/>
+      <c r="F2" s="207"/>
+      <c r="G2" s="207"/>
+      <c r="H2" s="208"/>
     </row>
     <row r="3" spans="1:9">
       <c r="A3" s="10"/>
       <c r="D3" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="206">
+      <c r="E3" s="210">
         <v>1153202676</v>
       </c>
-      <c r="F3" s="206"/>
-      <c r="G3" s="206"/>
-      <c r="H3" s="207"/>
+      <c r="F3" s="210"/>
+      <c r="G3" s="210"/>
+      <c r="H3" s="211"/>
     </row>
     <row r="4" spans="1:9">
       <c r="A4" s="10"/>
@@ -2333,7 +2330,7 @@
       <c r="A7" s="10"/>
       <c r="H7" s="11"/>
     </row>
-    <row r="8" spans="1:9" s="5" customFormat="1" ht="18.75">
+    <row r="8" spans="1:9" s="5" customFormat="1" ht="18">
       <c r="A8" s="18" t="s">
         <v>5</v>
       </c>
@@ -2376,14 +2373,14 @@
       <c r="H11" s="11"/>
     </row>
     <row r="12" spans="1:9" ht="67.5" hidden="1" customHeight="1">
-      <c r="A12" s="217"/>
-      <c r="B12" s="186"/>
-      <c r="C12" s="186"/>
-      <c r="D12" s="186"/>
-      <c r="E12" s="186"/>
-      <c r="F12" s="186"/>
-      <c r="G12" s="186"/>
-      <c r="H12" s="218"/>
+      <c r="A12" s="215"/>
+      <c r="B12" s="216"/>
+      <c r="C12" s="216"/>
+      <c r="D12" s="216"/>
+      <c r="E12" s="216"/>
+      <c r="F12" s="216"/>
+      <c r="G12" s="216"/>
+      <c r="H12" s="217"/>
     </row>
     <row r="13" spans="1:9" ht="13.5" customHeight="1">
       <c r="A13" s="12"/>
@@ -2395,17 +2392,17 @@
       <c r="G13" s="4"/>
       <c r="H13" s="13"/>
     </row>
-    <row r="14" spans="1:9" ht="15.75">
-      <c r="A14" s="219" t="s">
+    <row r="14" spans="1:9" ht="15.6">
+      <c r="A14" s="218" t="s">
         <v>121</v>
       </c>
-      <c r="B14" s="219"/>
-      <c r="C14" s="219"/>
-      <c r="D14" s="219"/>
-      <c r="E14" s="219"/>
-      <c r="F14" s="219"/>
-      <c r="G14" s="219"/>
-      <c r="H14" s="219"/>
+      <c r="B14" s="218"/>
+      <c r="C14" s="218"/>
+      <c r="D14" s="218"/>
+      <c r="E14" s="218"/>
+      <c r="F14" s="218"/>
+      <c r="G14" s="218"/>
+      <c r="H14" s="218"/>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" s="172" t="s">
@@ -2468,16 +2465,16 @@
       <c r="I18" s="7"/>
     </row>
     <row r="19" spans="1:9" hidden="1">
-      <c r="A19" s="213" t="s">
+      <c r="A19" s="214" t="s">
         <v>138</v>
       </c>
-      <c r="B19" s="213"/>
-      <c r="C19" s="213"/>
-      <c r="D19" s="213"/>
-      <c r="E19" s="213"/>
-      <c r="F19" s="213"/>
-      <c r="G19" s="213"/>
-      <c r="H19" s="213"/>
+      <c r="B19" s="214"/>
+      <c r="C19" s="214"/>
+      <c r="D19" s="214"/>
+      <c r="E19" s="214"/>
+      <c r="F19" s="214"/>
+      <c r="G19" s="214"/>
+      <c r="H19" s="214"/>
     </row>
     <row r="20" spans="1:9" hidden="1">
       <c r="A20" s="172" t="s">
@@ -2523,16 +2520,16 @@
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" s="212" t="s">
+      <c r="A23" s="213" t="s">
         <v>126</v>
       </c>
-      <c r="B23" s="212"/>
-      <c r="C23" s="212"/>
-      <c r="D23" s="212"/>
-      <c r="E23" s="212"/>
-      <c r="F23" s="212"/>
-      <c r="G23" s="212"/>
-      <c r="H23" s="212"/>
+      <c r="B23" s="213"/>
+      <c r="C23" s="213"/>
+      <c r="D23" s="213"/>
+      <c r="E23" s="213"/>
+      <c r="F23" s="213"/>
+      <c r="G23" s="213"/>
+      <c r="H23" s="213"/>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" s="137" t="s">
@@ -2575,16 +2572,16 @@
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" s="205" t="s">
+      <c r="A27" s="209" t="s">
         <v>86</v>
       </c>
-      <c r="B27" s="205"/>
-      <c r="C27" s="205"/>
-      <c r="D27" s="205"/>
-      <c r="E27" s="205"/>
-      <c r="F27" s="205"/>
-      <c r="G27" s="205"/>
-      <c r="H27" s="205"/>
+      <c r="B27" s="209"/>
+      <c r="C27" s="209"/>
+      <c r="D27" s="209"/>
+      <c r="E27" s="209"/>
+      <c r="F27" s="209"/>
+      <c r="G27" s="209"/>
+      <c r="H27" s="209"/>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="172"/>
@@ -2641,16 +2638,16 @@
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" s="205" t="s">
+      <c r="A32" s="209" t="s">
         <v>127</v>
       </c>
-      <c r="B32" s="205"/>
-      <c r="C32" s="205"/>
-      <c r="D32" s="205"/>
-      <c r="E32" s="205"/>
-      <c r="F32" s="205"/>
-      <c r="G32" s="205"/>
-      <c r="H32" s="205"/>
+      <c r="B32" s="209"/>
+      <c r="C32" s="209"/>
+      <c r="D32" s="209"/>
+      <c r="E32" s="209"/>
+      <c r="F32" s="209"/>
+      <c r="G32" s="209"/>
+      <c r="H32" s="209"/>
     </row>
     <row r="33" spans="1:10" ht="14.25" customHeight="1">
       <c r="A33" s="137" t="s">
@@ -2696,16 +2693,16 @@
       </c>
     </row>
     <row r="36" spans="1:10">
-      <c r="A36" s="219" t="s">
+      <c r="A36" s="218" t="s">
         <v>128</v>
       </c>
-      <c r="B36" s="219"/>
-      <c r="C36" s="219"/>
-      <c r="D36" s="219"/>
-      <c r="E36" s="219"/>
-      <c r="F36" s="219"/>
-      <c r="G36" s="219"/>
-      <c r="H36" s="219"/>
+      <c r="B36" s="218"/>
+      <c r="C36" s="218"/>
+      <c r="D36" s="218"/>
+      <c r="E36" s="218"/>
+      <c r="F36" s="218"/>
+      <c r="G36" s="218"/>
+      <c r="H36" s="218"/>
     </row>
     <row r="37" spans="1:10">
       <c r="A37" s="80" t="s">
@@ -2737,15 +2734,15 @@
       <c r="I38" s="7"/>
     </row>
     <row r="39" spans="1:10" ht="15.6" customHeight="1">
-      <c r="A39" s="214" t="s">
+      <c r="A39" s="203" t="s">
         <v>156</v>
       </c>
-      <c r="B39" s="215"/>
-      <c r="C39" s="215"/>
-      <c r="D39" s="215"/>
-      <c r="E39" s="215"/>
-      <c r="F39" s="215"/>
-      <c r="G39" s="216"/>
+      <c r="B39" s="204"/>
+      <c r="C39" s="204"/>
+      <c r="D39" s="204"/>
+      <c r="E39" s="204"/>
+      <c r="F39" s="204"/>
+      <c r="G39" s="205"/>
       <c r="H39" s="73">
         <f>71000+75400+57100</f>
         <v>203500</v>
@@ -2775,21 +2772,21 @@
       <c r="D41" s="82"/>
       <c r="E41" s="82"/>
       <c r="F41" s="82"/>
-      <c r="G41" s="243"/>
+      <c r="G41" s="186"/>
       <c r="H41" s="73">
         <v>45000</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="37.9" customHeight="1">
-      <c r="A42" s="223" t="s">
+    <row r="42" spans="1:10" ht="37.950000000000003" customHeight="1">
+      <c r="A42" s="187" t="s">
         <v>155</v>
       </c>
-      <c r="B42" s="224"/>
-      <c r="C42" s="224"/>
-      <c r="D42" s="224"/>
-      <c r="E42" s="224"/>
-      <c r="F42" s="224"/>
-      <c r="G42" s="225"/>
+      <c r="B42" s="188"/>
+      <c r="C42" s="188"/>
+      <c r="D42" s="188"/>
+      <c r="E42" s="188"/>
+      <c r="F42" s="188"/>
+      <c r="G42" s="189"/>
       <c r="H42" s="73">
         <v>55400</v>
       </c>
@@ -2838,16 +2835,16 @@
       </c>
     </row>
     <row r="46" spans="1:10">
-      <c r="A46" s="219" t="s">
+      <c r="A46" s="218" t="s">
         <v>129</v>
       </c>
-      <c r="B46" s="219"/>
-      <c r="C46" s="219"/>
-      <c r="D46" s="219"/>
-      <c r="E46" s="219"/>
-      <c r="F46" s="219"/>
-      <c r="G46" s="219"/>
-      <c r="H46" s="219"/>
+      <c r="B46" s="218"/>
+      <c r="C46" s="218"/>
+      <c r="D46" s="218"/>
+      <c r="E46" s="218"/>
+      <c r="F46" s="218"/>
+      <c r="G46" s="218"/>
+      <c r="H46" s="218"/>
     </row>
     <row r="47" spans="1:10">
       <c r="A47" s="137" t="s">
@@ -2897,16 +2894,16 @@
       <c r="K49" s="7"/>
     </row>
     <row r="50" spans="1:11" s="6" customFormat="1">
-      <c r="A50" s="220" t="s">
+      <c r="A50" s="190" t="s">
         <v>130</v>
       </c>
-      <c r="B50" s="221"/>
-      <c r="C50" s="221"/>
-      <c r="D50" s="221"/>
-      <c r="E50" s="221"/>
-      <c r="F50" s="221"/>
-      <c r="G50" s="221"/>
-      <c r="H50" s="222"/>
+      <c r="B50" s="191"/>
+      <c r="C50" s="191"/>
+      <c r="D50" s="191"/>
+      <c r="E50" s="191"/>
+      <c r="F50" s="191"/>
+      <c r="G50" s="191"/>
+      <c r="H50" s="192"/>
     </row>
     <row r="51" spans="1:11" s="6" customFormat="1">
       <c r="A51" s="80" t="s">
@@ -2939,16 +2936,16 @@
       </c>
     </row>
     <row r="53" spans="1:11" s="6" customFormat="1">
-      <c r="A53" s="219" t="s">
+      <c r="A53" s="218" t="s">
         <v>131</v>
       </c>
-      <c r="B53" s="219"/>
-      <c r="C53" s="219"/>
-      <c r="D53" s="219"/>
-      <c r="E53" s="219"/>
-      <c r="F53" s="219"/>
-      <c r="G53" s="219"/>
-      <c r="H53" s="219"/>
+      <c r="B53" s="218"/>
+      <c r="C53" s="218"/>
+      <c r="D53" s="218"/>
+      <c r="E53" s="218"/>
+      <c r="F53" s="218"/>
+      <c r="G53" s="218"/>
+      <c r="H53" s="218"/>
     </row>
     <row r="54" spans="1:11" s="6" customFormat="1">
       <c r="A54" s="80" t="s">
@@ -2965,15 +2962,15 @@
       </c>
     </row>
     <row r="55" spans="1:11" s="6" customFormat="1" ht="31.5" customHeight="1">
-      <c r="A55" s="214" t="s">
+      <c r="A55" s="203" t="s">
         <v>159</v>
       </c>
-      <c r="B55" s="215"/>
-      <c r="C55" s="215"/>
-      <c r="D55" s="215"/>
-      <c r="E55" s="215"/>
-      <c r="F55" s="215"/>
-      <c r="G55" s="216"/>
+      <c r="B55" s="204"/>
+      <c r="C55" s="204"/>
+      <c r="D55" s="204"/>
+      <c r="E55" s="204"/>
+      <c r="F55" s="204"/>
+      <c r="G55" s="205"/>
       <c r="H55" s="73">
         <v>997000</v>
       </c>
@@ -2995,14 +2992,14 @@
       <c r="I56" s="60"/>
     </row>
     <row r="57" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A57" s="220"/>
-      <c r="B57" s="221"/>
-      <c r="C57" s="221"/>
-      <c r="D57" s="221"/>
-      <c r="E57" s="221"/>
-      <c r="F57" s="221"/>
-      <c r="G57" s="221"/>
-      <c r="H57" s="222"/>
+      <c r="A57" s="190"/>
+      <c r="B57" s="191"/>
+      <c r="C57" s="191"/>
+      <c r="D57" s="191"/>
+      <c r="E57" s="191"/>
+      <c r="F57" s="191"/>
+      <c r="G57" s="191"/>
+      <c r="H57" s="192"/>
     </row>
     <row r="58" spans="1:11" s="6" customFormat="1" ht="23.25" hidden="1" customHeight="1">
       <c r="A58" s="81"/>
@@ -3042,60 +3039,60 @@
       </c>
     </row>
     <row r="61" spans="1:11" s="6" customFormat="1" ht="18" hidden="1" customHeight="1">
-      <c r="A61" s="226" t="s">
+      <c r="A61" s="196" t="s">
         <v>80</v>
       </c>
-      <c r="B61" s="227"/>
-      <c r="C61" s="227"/>
-      <c r="D61" s="227"/>
-      <c r="E61" s="227"/>
-      <c r="F61" s="227"/>
-      <c r="G61" s="227"/>
+      <c r="B61" s="197"/>
+      <c r="C61" s="197"/>
+      <c r="D61" s="197"/>
+      <c r="E61" s="197"/>
+      <c r="F61" s="197"/>
+      <c r="G61" s="197"/>
       <c r="H61" s="162">
         <f>H56</f>
         <v>1097000</v>
       </c>
     </row>
     <row r="62" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A62" s="229"/>
-      <c r="B62" s="229"/>
-      <c r="C62" s="229"/>
-      <c r="D62" s="229"/>
-      <c r="E62" s="229"/>
-      <c r="F62" s="229"/>
-      <c r="G62" s="229"/>
-      <c r="H62" s="229"/>
+      <c r="A62" s="201"/>
+      <c r="B62" s="201"/>
+      <c r="C62" s="201"/>
+      <c r="D62" s="201"/>
+      <c r="E62" s="201"/>
+      <c r="F62" s="201"/>
+      <c r="G62" s="201"/>
+      <c r="H62" s="201"/>
     </row>
     <row r="63" spans="1:11" s="6" customFormat="1" ht="86.25" hidden="1" customHeight="1">
-      <c r="A63" s="230"/>
-      <c r="B63" s="230"/>
-      <c r="C63" s="230"/>
-      <c r="D63" s="230"/>
-      <c r="E63" s="230"/>
-      <c r="F63" s="230"/>
-      <c r="G63" s="230"/>
-      <c r="H63" s="230"/>
+      <c r="A63" s="202"/>
+      <c r="B63" s="202"/>
+      <c r="C63" s="202"/>
+      <c r="D63" s="202"/>
+      <c r="E63" s="202"/>
+      <c r="F63" s="202"/>
+      <c r="G63" s="202"/>
+      <c r="H63" s="202"/>
     </row>
     <row r="64" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
-      <c r="A64" s="228" t="s">
+      <c r="A64" s="200" t="s">
         <v>82</v>
       </c>
-      <c r="B64" s="228"/>
-      <c r="C64" s="228"/>
-      <c r="D64" s="228"/>
-      <c r="E64" s="228"/>
-      <c r="F64" s="228"/>
-      <c r="G64" s="228"/>
+      <c r="B64" s="200"/>
+      <c r="C64" s="200"/>
+      <c r="D64" s="200"/>
+      <c r="E64" s="200"/>
+      <c r="F64" s="200"/>
+      <c r="G64" s="200"/>
       <c r="H64" s="163"/>
     </row>
     <row r="65" spans="1:11" s="6" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A65" s="214"/>
-      <c r="B65" s="215"/>
-      <c r="C65" s="215"/>
-      <c r="D65" s="215"/>
-      <c r="E65" s="215"/>
-      <c r="F65" s="215"/>
-      <c r="G65" s="216"/>
+      <c r="A65" s="203"/>
+      <c r="B65" s="204"/>
+      <c r="C65" s="204"/>
+      <c r="D65" s="204"/>
+      <c r="E65" s="204"/>
+      <c r="F65" s="204"/>
+      <c r="G65" s="205"/>
       <c r="H65" s="73"/>
     </row>
     <row r="66" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1">
@@ -3124,57 +3121,57 @@
       <c r="H67" s="129"/>
     </row>
     <row r="68" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A68" s="193" t="s">
+      <c r="A68" s="198" t="s">
         <v>81</v>
       </c>
-      <c r="B68" s="194"/>
-      <c r="C68" s="194"/>
-      <c r="D68" s="194"/>
-      <c r="E68" s="194"/>
-      <c r="F68" s="194"/>
-      <c r="G68" s="194"/>
+      <c r="B68" s="199"/>
+      <c r="C68" s="199"/>
+      <c r="D68" s="199"/>
+      <c r="E68" s="199"/>
+      <c r="F68" s="199"/>
+      <c r="G68" s="199"/>
       <c r="H68" s="130">
         <f>H66</f>
         <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A69" s="209" t="s">
+      <c r="A69" s="193" t="s">
         <v>87</v>
       </c>
-      <c r="B69" s="210"/>
-      <c r="C69" s="210"/>
-      <c r="D69" s="210"/>
-      <c r="E69" s="210"/>
-      <c r="F69" s="210"/>
-      <c r="G69" s="211"/>
+      <c r="B69" s="194"/>
+      <c r="C69" s="194"/>
+      <c r="D69" s="194"/>
+      <c r="E69" s="194"/>
+      <c r="F69" s="194"/>
+      <c r="G69" s="195"/>
       <c r="H69" s="130">
         <f>3283892.26-2477720.36</f>
         <v>806171.89999999991</v>
       </c>
     </row>
     <row r="70" spans="1:11" s="6" customFormat="1" ht="18" customHeight="1" thickBot="1">
-      <c r="A70" s="209" t="s">
+      <c r="A70" s="193" t="s">
         <v>92</v>
       </c>
-      <c r="B70" s="210"/>
-      <c r="C70" s="210"/>
-      <c r="D70" s="210"/>
-      <c r="E70" s="210"/>
-      <c r="F70" s="210"/>
-      <c r="G70" s="211"/>
+      <c r="B70" s="194"/>
+      <c r="C70" s="194"/>
+      <c r="D70" s="194"/>
+      <c r="E70" s="194"/>
+      <c r="F70" s="194"/>
+      <c r="G70" s="195"/>
       <c r="H70" s="130"/>
     </row>
-    <row r="71" spans="1:11" ht="18.75">
-      <c r="A71" s="193" t="s">
+    <row r="71" spans="1:11" ht="18">
+      <c r="A71" s="198" t="s">
         <v>88</v>
       </c>
-      <c r="B71" s="194"/>
-      <c r="C71" s="194"/>
-      <c r="D71" s="194"/>
-      <c r="E71" s="194"/>
-      <c r="F71" s="194"/>
-      <c r="G71" s="194"/>
+      <c r="B71" s="199"/>
+      <c r="C71" s="199"/>
+      <c r="D71" s="199"/>
+      <c r="E71" s="199"/>
+      <c r="F71" s="199"/>
+      <c r="G71" s="199"/>
       <c r="H71" s="130">
         <f>H26+H35+H45+H49+H52+H31+H18+H22</f>
         <v>2477720.36</v>
@@ -3182,34 +3179,34 @@
       <c r="J71" s="171"/>
       <c r="K71" s="142"/>
     </row>
-    <row r="72" spans="1:11" ht="18.75">
-      <c r="A72" s="199" t="s">
+    <row r="72" spans="1:11" ht="18">
+      <c r="A72" s="229" t="s">
         <v>119</v>
       </c>
-      <c r="B72" s="200"/>
-      <c r="C72" s="200"/>
-      <c r="D72" s="200"/>
-      <c r="E72" s="200"/>
-      <c r="F72" s="200"/>
-      <c r="G72" s="201"/>
+      <c r="B72" s="230"/>
+      <c r="C72" s="230"/>
+      <c r="D72" s="230"/>
+      <c r="E72" s="230"/>
+      <c r="F72" s="230"/>
+      <c r="G72" s="231"/>
       <c r="H72" s="131">
         <f>H69+H71</f>
         <v>3283892.26</v>
       </c>
       <c r="I72" s="126"/>
-      <c r="J72" s="208"/>
-      <c r="K72" s="208"/>
-    </row>
-    <row r="73" spans="1:11" ht="18.75">
-      <c r="A73" s="199" t="s">
+      <c r="J72" s="212"/>
+      <c r="K72" s="212"/>
+    </row>
+    <row r="73" spans="1:11" ht="18">
+      <c r="A73" s="229" t="s">
         <v>93</v>
       </c>
-      <c r="B73" s="200"/>
-      <c r="C73" s="200"/>
-      <c r="D73" s="200"/>
-      <c r="E73" s="200"/>
-      <c r="F73" s="200"/>
-      <c r="G73" s="201"/>
+      <c r="B73" s="230"/>
+      <c r="C73" s="230"/>
+      <c r="D73" s="230"/>
+      <c r="E73" s="230"/>
+      <c r="F73" s="230"/>
+      <c r="G73" s="231"/>
       <c r="H73" s="132">
         <f>H70+H68</f>
         <v>0</v>
@@ -3217,38 +3214,38 @@
       <c r="J73" s="142"/>
     </row>
     <row r="74" spans="1:11" ht="20.25" customHeight="1" thickBot="1">
-      <c r="A74" s="197" t="s">
+      <c r="A74" s="227" t="s">
         <v>83</v>
       </c>
-      <c r="B74" s="198"/>
-      <c r="C74" s="198"/>
-      <c r="D74" s="198"/>
-      <c r="E74" s="198"/>
-      <c r="F74" s="198"/>
-      <c r="G74" s="198"/>
+      <c r="B74" s="228"/>
+      <c r="C74" s="228"/>
+      <c r="D74" s="228"/>
+      <c r="E74" s="228"/>
+      <c r="F74" s="228"/>
+      <c r="G74" s="228"/>
       <c r="H74" s="133">
         <f>H71+H68</f>
         <v>2477720.36</v>
       </c>
       <c r="J74" s="7"/>
     </row>
-    <row r="75" spans="1:11" ht="18.75" hidden="1">
-      <c r="A75" s="195" t="s">
+    <row r="75" spans="1:11" ht="18" hidden="1">
+      <c r="A75" s="225" t="s">
         <v>17</v>
       </c>
-      <c r="B75" s="196"/>
-      <c r="C75" s="196"/>
-      <c r="D75" s="196"/>
-      <c r="E75" s="196"/>
-      <c r="F75" s="196"/>
-      <c r="G75" s="196"/>
+      <c r="B75" s="226"/>
+      <c r="C75" s="226"/>
+      <c r="D75" s="226"/>
+      <c r="E75" s="226"/>
+      <c r="F75" s="226"/>
+      <c r="G75" s="226"/>
       <c r="H75" s="134">
         <f>H60</f>
         <v>0</v>
       </c>
       <c r="J75" s="7"/>
     </row>
-    <row r="76" spans="1:11" ht="18.75" hidden="1">
+    <row r="76" spans="1:11" ht="18" hidden="1">
       <c r="A76" s="135"/>
       <c r="B76" s="135"/>
       <c r="C76" s="135"/>
@@ -3259,7 +3256,7 @@
       <c r="H76" s="136"/>
       <c r="J76" s="7"/>
     </row>
-    <row r="77" spans="1:11" ht="18.75" hidden="1">
+    <row r="77" spans="1:11" ht="18" hidden="1">
       <c r="A77" s="135"/>
       <c r="B77" s="135"/>
       <c r="C77" s="135"/>
@@ -3270,7 +3267,7 @@
       <c r="H77" s="136"/>
       <c r="J77" s="7"/>
     </row>
-    <row r="78" spans="1:11" ht="18.75" hidden="1">
+    <row r="78" spans="1:11" ht="18" hidden="1">
       <c r="A78" s="135"/>
       <c r="B78" s="135"/>
       <c r="C78" s="135"/>
@@ -3291,19 +3288,19 @@
       <c r="G79" s="137"/>
       <c r="H79" s="137"/>
     </row>
-    <row r="80" spans="1:11" ht="18.75">
-      <c r="A80" s="190" t="s">
+    <row r="80" spans="1:11" ht="18">
+      <c r="A80" s="222" t="s">
         <v>10</v>
       </c>
-      <c r="B80" s="191"/>
-      <c r="C80" s="191"/>
-      <c r="D80" s="191"/>
-      <c r="E80" s="191"/>
-      <c r="F80" s="191"/>
-      <c r="G80" s="191"/>
-      <c r="H80" s="192"/>
-    </row>
-    <row r="81" spans="1:11" ht="18.75">
+      <c r="B80" s="223"/>
+      <c r="C80" s="223"/>
+      <c r="D80" s="223"/>
+      <c r="E80" s="223"/>
+      <c r="F80" s="223"/>
+      <c r="G80" s="223"/>
+      <c r="H80" s="224"/>
+    </row>
+    <row r="81" spans="1:11" ht="18">
       <c r="A81" s="138" t="s">
         <v>12</v>
       </c>
@@ -3406,7 +3403,7 @@
       <c r="G87" s="4"/>
       <c r="H87" s="98"/>
     </row>
-    <row r="88" spans="1:11" ht="18.75">
+    <row r="88" spans="1:11" ht="18">
       <c r="A88" s="22" t="s">
         <v>11</v>
       </c>
@@ -3421,20 +3418,20 @@
         <v>4229401.2367692199</v>
       </c>
     </row>
-    <row r="89" spans="1:11" ht="15.75" thickBot="1"/>
-    <row r="90" spans="1:11" ht="16.5" thickBot="1">
-      <c r="A90" s="187" t="s">
+    <row r="89" spans="1:11" ht="15" thickBot="1"/>
+    <row r="90" spans="1:11" ht="16.2" thickBot="1">
+      <c r="A90" s="219" t="s">
         <v>97</v>
       </c>
-      <c r="B90" s="188"/>
-      <c r="C90" s="188"/>
-      <c r="D90" s="188"/>
-      <c r="E90" s="188"/>
-      <c r="F90" s="188"/>
-      <c r="G90" s="188"/>
-      <c r="H90" s="189"/>
-    </row>
-    <row r="91" spans="1:11" ht="15.75">
+      <c r="B90" s="220"/>
+      <c r="C90" s="220"/>
+      <c r="D90" s="220"/>
+      <c r="E90" s="220"/>
+      <c r="F90" s="220"/>
+      <c r="G90" s="220"/>
+      <c r="H90" s="221"/>
+    </row>
+    <row r="91" spans="1:11" ht="15.6">
       <c r="A91" s="87" t="s">
         <v>12</v>
       </c>
@@ -3496,55 +3493,55 @@
       </c>
     </row>
     <row r="98" spans="1:8" hidden="1">
-      <c r="A98" s="186"/>
-      <c r="B98" s="186"/>
-      <c r="C98" s="186"/>
-      <c r="D98" s="186"/>
-      <c r="E98" s="186"/>
-      <c r="F98" s="186"/>
-      <c r="G98" s="186"/>
-      <c r="H98" s="186"/>
+      <c r="A98" s="216"/>
+      <c r="B98" s="216"/>
+      <c r="C98" s="216"/>
+      <c r="D98" s="216"/>
+      <c r="E98" s="216"/>
+      <c r="F98" s="216"/>
+      <c r="G98" s="216"/>
+      <c r="H98" s="216"/>
     </row>
     <row r="99" spans="1:8" hidden="1">
-      <c r="A99" s="186"/>
-      <c r="B99" s="186"/>
-      <c r="C99" s="186"/>
-      <c r="D99" s="186"/>
-      <c r="E99" s="186"/>
-      <c r="F99" s="186"/>
-      <c r="G99" s="186"/>
-      <c r="H99" s="186"/>
+      <c r="A99" s="216"/>
+      <c r="B99" s="216"/>
+      <c r="C99" s="216"/>
+      <c r="D99" s="216"/>
+      <c r="E99" s="216"/>
+      <c r="F99" s="216"/>
+      <c r="G99" s="216"/>
+      <c r="H99" s="216"/>
     </row>
     <row r="100" spans="1:8" hidden="1">
-      <c r="A100" s="186"/>
-      <c r="B100" s="186"/>
-      <c r="C100" s="186"/>
-      <c r="D100" s="186"/>
-      <c r="E100" s="186"/>
-      <c r="F100" s="186"/>
-      <c r="G100" s="186"/>
-      <c r="H100" s="186"/>
+      <c r="A100" s="216"/>
+      <c r="B100" s="216"/>
+      <c r="C100" s="216"/>
+      <c r="D100" s="216"/>
+      <c r="E100" s="216"/>
+      <c r="F100" s="216"/>
+      <c r="G100" s="216"/>
+      <c r="H100" s="216"/>
     </row>
     <row r="101" spans="1:8" hidden="1">
-      <c r="A101" s="186"/>
-      <c r="B101" s="186"/>
-      <c r="C101" s="186"/>
-      <c r="D101" s="186"/>
-      <c r="E101" s="186"/>
-      <c r="F101" s="186"/>
-      <c r="G101" s="186"/>
-      <c r="H101" s="186"/>
+      <c r="A101" s="216"/>
+      <c r="B101" s="216"/>
+      <c r="C101" s="216"/>
+      <c r="D101" s="216"/>
+      <c r="E101" s="216"/>
+      <c r="F101" s="216"/>
+      <c r="G101" s="216"/>
+      <c r="H101" s="216"/>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="A42:G42"/>
-    <mergeCell ref="A50:H50"/>
-    <mergeCell ref="A69:G69"/>
-    <mergeCell ref="A61:G61"/>
-    <mergeCell ref="A68:G68"/>
-    <mergeCell ref="A64:G64"/>
-    <mergeCell ref="A62:H63"/>
-    <mergeCell ref="A55:G55"/>
+    <mergeCell ref="A98:H101"/>
+    <mergeCell ref="A90:H90"/>
+    <mergeCell ref="A80:H80"/>
+    <mergeCell ref="A71:G71"/>
+    <mergeCell ref="A75:G75"/>
+    <mergeCell ref="A74:G74"/>
+    <mergeCell ref="A73:G73"/>
+    <mergeCell ref="A72:G72"/>
     <mergeCell ref="D2:H2"/>
     <mergeCell ref="A27:H27"/>
     <mergeCell ref="E3:H3"/>
@@ -3561,14 +3558,14 @@
     <mergeCell ref="A36:H36"/>
     <mergeCell ref="A46:H46"/>
     <mergeCell ref="A39:G39"/>
-    <mergeCell ref="A98:H101"/>
-    <mergeCell ref="A90:H90"/>
-    <mergeCell ref="A80:H80"/>
-    <mergeCell ref="A71:G71"/>
-    <mergeCell ref="A75:G75"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A73:G73"/>
-    <mergeCell ref="A72:G72"/>
+    <mergeCell ref="A42:G42"/>
+    <mergeCell ref="A50:H50"/>
+    <mergeCell ref="A69:G69"/>
+    <mergeCell ref="A61:G61"/>
+    <mergeCell ref="A68:G68"/>
+    <mergeCell ref="A64:G64"/>
+    <mergeCell ref="A62:H63"/>
+    <mergeCell ref="A55:G55"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup scale="85" orientation="landscape" r:id="rId1"/>
@@ -3579,24 +3576,24 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:R41"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" customWidth="1"/>
-    <col min="2" max="2" width="9.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.85546875" customWidth="1"/>
-    <col min="4" max="4" width="7.85546875" customWidth="1"/>
+    <col min="1" max="1" width="4.5546875" customWidth="1"/>
+    <col min="2" max="2" width="9.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.88671875" customWidth="1"/>
+    <col min="4" max="4" width="7.88671875" customWidth="1"/>
     <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="15.28515625" style="2" customWidth="1"/>
-    <col min="7" max="8" width="12.28515625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="2" customWidth="1"/>
+    <col min="6" max="6" width="15.33203125" style="2" customWidth="1"/>
+    <col min="7" max="8" width="12.33203125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="12.5546875" style="2" customWidth="1"/>
     <col min="10" max="10" width="11" style="2" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" style="2" customWidth="1"/>
-    <col min="12" max="12" width="13.7109375" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.5703125" customWidth="1"/>
-    <col min="14" max="14" width="13.42578125" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="15.140625" customWidth="1"/>
+    <col min="11" max="11" width="13.33203125" style="2" customWidth="1"/>
+    <col min="12" max="12" width="13.6640625" style="2" customWidth="1"/>
+    <col min="13" max="13" width="14.5546875" customWidth="1"/>
+    <col min="14" max="14" width="13.44140625" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="15.109375" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" ht="26.25" customHeight="1">
@@ -3692,16 +3689,16 @@
     </row>
     <row r="5" spans="1:17" ht="15.75" customHeight="1">
       <c r="A5" s="120"/>
-      <c r="B5" s="232">
+      <c r="B5" s="233">
         <f>C2</f>
         <v>3283892.26</v>
       </c>
-      <c r="C5" s="232"/>
+      <c r="C5" s="233"/>
       <c r="D5" s="21"/>
-      <c r="E5" s="238">
+      <c r="E5" s="239">
         <v>1097000</v>
       </c>
-      <c r="F5" s="239"/>
+      <c r="F5" s="240"/>
       <c r="G5" s="114"/>
       <c r="H5" s="114"/>
       <c r="I5" s="114"/>
@@ -3714,13 +3711,13 @@
     </row>
     <row r="6" spans="1:17" ht="15.75" customHeight="1">
       <c r="A6" s="120"/>
-      <c r="B6" s="234"/>
-      <c r="C6" s="235"/>
+      <c r="B6" s="235"/>
+      <c r="C6" s="236"/>
       <c r="D6" s="21"/>
-      <c r="E6" s="234" t="s">
+      <c r="E6" s="235" t="s">
         <v>146</v>
       </c>
-      <c r="F6" s="235"/>
+      <c r="F6" s="236"/>
       <c r="G6" s="114"/>
       <c r="H6" s="114"/>
       <c r="I6" s="114"/>
@@ -3733,11 +3730,11 @@
     </row>
     <row r="7" spans="1:17" ht="18.75" customHeight="1">
       <c r="A7" s="120"/>
-      <c r="B7" s="232"/>
-      <c r="C7" s="232"/>
+      <c r="B7" s="233"/>
+      <c r="C7" s="233"/>
       <c r="D7" s="21"/>
-      <c r="E7" s="236"/>
-      <c r="F7" s="237"/>
+      <c r="E7" s="237"/>
+      <c r="F7" s="238"/>
       <c r="G7" s="114"/>
       <c r="H7" s="114"/>
       <c r="I7" s="114"/>
@@ -5076,7 +5073,7 @@
         <v>175829.73672799996</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="15.75">
+    <row r="32" spans="1:18" ht="15.6">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
@@ -5128,119 +5125,119 @@
     </row>
     <row r="33" spans="1:15" ht="14.25" customHeight="1"/>
     <row r="34" spans="1:15" hidden="1">
-      <c r="B34" s="231"/>
-      <c r="C34" s="231"/>
-      <c r="D34" s="231"/>
-      <c r="E34" s="231"/>
-      <c r="F34" s="231"/>
-      <c r="G34" s="231"/>
-      <c r="H34" s="231"/>
-      <c r="I34" s="231"/>
-      <c r="J34" s="231"/>
-      <c r="K34" s="231"/>
-      <c r="L34" s="231"/>
-      <c r="M34" s="231"/>
-      <c r="N34" s="231"/>
-      <c r="O34" s="231"/>
+      <c r="B34" s="232"/>
+      <c r="C34" s="232"/>
+      <c r="D34" s="232"/>
+      <c r="E34" s="232"/>
+      <c r="F34" s="232"/>
+      <c r="G34" s="232"/>
+      <c r="H34" s="232"/>
+      <c r="I34" s="232"/>
+      <c r="J34" s="232"/>
+      <c r="K34" s="232"/>
+      <c r="L34" s="232"/>
+      <c r="M34" s="232"/>
+      <c r="N34" s="232"/>
+      <c r="O34" s="232"/>
     </row>
     <row r="35" spans="1:15" hidden="1">
-      <c r="B35" s="231"/>
-      <c r="C35" s="231"/>
-      <c r="D35" s="231"/>
-      <c r="E35" s="231"/>
-      <c r="F35" s="231"/>
-      <c r="G35" s="231"/>
-      <c r="H35" s="231"/>
-      <c r="I35" s="231"/>
-      <c r="J35" s="231"/>
-      <c r="K35" s="231"/>
-      <c r="L35" s="231"/>
-      <c r="M35" s="231"/>
-      <c r="N35" s="231"/>
-      <c r="O35" s="231"/>
+      <c r="B35" s="232"/>
+      <c r="C35" s="232"/>
+      <c r="D35" s="232"/>
+      <c r="E35" s="232"/>
+      <c r="F35" s="232"/>
+      <c r="G35" s="232"/>
+      <c r="H35" s="232"/>
+      <c r="I35" s="232"/>
+      <c r="J35" s="232"/>
+      <c r="K35" s="232"/>
+      <c r="L35" s="232"/>
+      <c r="M35" s="232"/>
+      <c r="N35" s="232"/>
+      <c r="O35" s="232"/>
     </row>
     <row r="36" spans="1:15" hidden="1">
-      <c r="B36" s="231"/>
-      <c r="C36" s="231"/>
-      <c r="D36" s="231"/>
-      <c r="E36" s="231"/>
-      <c r="F36" s="231"/>
-      <c r="G36" s="231"/>
-      <c r="H36" s="231"/>
-      <c r="I36" s="231"/>
-      <c r="J36" s="231"/>
-      <c r="K36" s="231"/>
-      <c r="L36" s="231"/>
-      <c r="M36" s="231"/>
-      <c r="N36" s="231"/>
-      <c r="O36" s="231"/>
+      <c r="B36" s="232"/>
+      <c r="C36" s="232"/>
+      <c r="D36" s="232"/>
+      <c r="E36" s="232"/>
+      <c r="F36" s="232"/>
+      <c r="G36" s="232"/>
+      <c r="H36" s="232"/>
+      <c r="I36" s="232"/>
+      <c r="J36" s="232"/>
+      <c r="K36" s="232"/>
+      <c r="L36" s="232"/>
+      <c r="M36" s="232"/>
+      <c r="N36" s="232"/>
+      <c r="O36" s="232"/>
     </row>
     <row r="37" spans="1:15" hidden="1">
-      <c r="B37" s="231"/>
-      <c r="C37" s="231"/>
-      <c r="D37" s="231"/>
-      <c r="E37" s="231"/>
-      <c r="F37" s="231"/>
-      <c r="G37" s="231"/>
-      <c r="H37" s="231"/>
-      <c r="I37" s="231"/>
-      <c r="J37" s="231"/>
-      <c r="K37" s="231"/>
-      <c r="L37" s="231"/>
-      <c r="M37" s="231"/>
-      <c r="N37" s="231"/>
-      <c r="O37" s="231"/>
+      <c r="B37" s="232"/>
+      <c r="C37" s="232"/>
+      <c r="D37" s="232"/>
+      <c r="E37" s="232"/>
+      <c r="F37" s="232"/>
+      <c r="G37" s="232"/>
+      <c r="H37" s="232"/>
+      <c r="I37" s="232"/>
+      <c r="J37" s="232"/>
+      <c r="K37" s="232"/>
+      <c r="L37" s="232"/>
+      <c r="M37" s="232"/>
+      <c r="N37" s="232"/>
+      <c r="O37" s="232"/>
     </row>
     <row r="38" spans="1:15" hidden="1">
-      <c r="A38" s="233"/>
-      <c r="B38" s="233"/>
-      <c r="C38" s="233"/>
-      <c r="D38" s="233"/>
-      <c r="E38" s="233"/>
-      <c r="F38" s="233"/>
-      <c r="G38" s="233"/>
-      <c r="H38" s="233"/>
-      <c r="I38" s="233"/>
-      <c r="J38" s="233"/>
-      <c r="K38" s="233"/>
-      <c r="L38" s="233"/>
-      <c r="M38" s="233"/>
-      <c r="N38" s="233"/>
-      <c r="O38" s="233"/>
+      <c r="A38" s="234"/>
+      <c r="B38" s="234"/>
+      <c r="C38" s="234"/>
+      <c r="D38" s="234"/>
+      <c r="E38" s="234"/>
+      <c r="F38" s="234"/>
+      <c r="G38" s="234"/>
+      <c r="H38" s="234"/>
+      <c r="I38" s="234"/>
+      <c r="J38" s="234"/>
+      <c r="K38" s="234"/>
+      <c r="L38" s="234"/>
+      <c r="M38" s="234"/>
+      <c r="N38" s="234"/>
+      <c r="O38" s="234"/>
     </row>
     <row r="39" spans="1:15" hidden="1">
-      <c r="A39" s="233"/>
-      <c r="B39" s="233"/>
-      <c r="C39" s="233"/>
-      <c r="D39" s="233"/>
-      <c r="E39" s="233"/>
-      <c r="F39" s="233"/>
-      <c r="G39" s="233"/>
-      <c r="H39" s="233"/>
-      <c r="I39" s="233"/>
-      <c r="J39" s="233"/>
-      <c r="K39" s="233"/>
-      <c r="L39" s="233"/>
-      <c r="M39" s="233"/>
-      <c r="N39" s="233"/>
-      <c r="O39" s="233"/>
+      <c r="A39" s="234"/>
+      <c r="B39" s="234"/>
+      <c r="C39" s="234"/>
+      <c r="D39" s="234"/>
+      <c r="E39" s="234"/>
+      <c r="F39" s="234"/>
+      <c r="G39" s="234"/>
+      <c r="H39" s="234"/>
+      <c r="I39" s="234"/>
+      <c r="J39" s="234"/>
+      <c r="K39" s="234"/>
+      <c r="L39" s="234"/>
+      <c r="M39" s="234"/>
+      <c r="N39" s="234"/>
+      <c r="O39" s="234"/>
     </row>
     <row r="40" spans="1:15" hidden="1">
-      <c r="A40" s="233"/>
-      <c r="B40" s="233"/>
-      <c r="C40" s="233"/>
-      <c r="D40" s="233"/>
-      <c r="E40" s="233"/>
-      <c r="F40" s="233"/>
-      <c r="G40" s="233"/>
-      <c r="H40" s="233"/>
-      <c r="I40" s="233"/>
-      <c r="J40" s="233"/>
-      <c r="K40" s="233"/>
-      <c r="L40" s="233"/>
-      <c r="M40" s="233"/>
-      <c r="N40" s="233"/>
-      <c r="O40" s="233"/>
+      <c r="A40" s="234"/>
+      <c r="B40" s="234"/>
+      <c r="C40" s="234"/>
+      <c r="D40" s="234"/>
+      <c r="E40" s="234"/>
+      <c r="F40" s="234"/>
+      <c r="G40" s="234"/>
+      <c r="H40" s="234"/>
+      <c r="I40" s="234"/>
+      <c r="J40" s="234"/>
+      <c r="K40" s="234"/>
+      <c r="L40" s="234"/>
+      <c r="M40" s="234"/>
+      <c r="N40" s="234"/>
+      <c r="O40" s="234"/>
     </row>
     <row r="41" spans="1:15">
       <c r="O41" s="7"/>
@@ -5265,25 +5262,25 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G34"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="4.140625" customWidth="1"/>
-    <col min="3" max="3" width="19.28515625" customWidth="1"/>
+    <col min="1" max="1" width="4.109375" customWidth="1"/>
+    <col min="3" max="3" width="19.33203125" customWidth="1"/>
     <col min="5" max="5" width="18" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.28515625" customWidth="1"/>
-    <col min="7" max="7" width="11.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.33203125" customWidth="1"/>
+    <col min="7" max="7" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="34.5" customHeight="1" thickBot="1">
-      <c r="A1" s="240" t="s">
+      <c r="A1" s="241" t="s">
         <v>90</v>
       </c>
-      <c r="B1" s="241"/>
-      <c r="C1" s="241"/>
-      <c r="D1" s="241"/>
-      <c r="E1" s="241"/>
-      <c r="F1" s="241"/>
-      <c r="G1" s="242"/>
+      <c r="B1" s="242"/>
+      <c r="C1" s="242"/>
+      <c r="D1" s="242"/>
+      <c r="E1" s="242"/>
+      <c r="F1" s="242"/>
+      <c r="G1" s="243"/>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="30"/>
@@ -5319,13 +5316,13 @@
       <c r="C6" s="16"/>
       <c r="G6" s="31"/>
     </row>
-    <row r="7" spans="1:7" ht="15.75" thickBot="1">
+    <row r="7" spans="1:7" ht="15" thickBot="1">
       <c r="A7" s="62"/>
       <c r="B7" s="32"/>
       <c r="C7" s="16"/>
       <c r="G7" s="31"/>
     </row>
-    <row r="8" spans="1:7" ht="30.75" thickBot="1">
+    <row r="8" spans="1:7" ht="29.4" thickBot="1">
       <c r="A8" s="26" t="s">
         <v>0</v>
       </c>
@@ -5686,7 +5683,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="15.75">
+    <row r="24" spans="1:7" ht="15.6">
       <c r="A24" s="51">
         <v>16</v>
       </c>
@@ -5708,7 +5705,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="25" spans="1:7" ht="15.75">
+    <row r="25" spans="1:7" ht="15.6">
       <c r="A25" s="51">
         <v>17</v>
       </c>
@@ -5730,7 +5727,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:7" ht="15.75">
+    <row r="26" spans="1:7" ht="15.6">
       <c r="A26" s="51">
         <v>18</v>
       </c>
@@ -5752,7 +5749,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="27" spans="1:7" ht="15.75">
+    <row r="27" spans="1:7" ht="15.6">
       <c r="A27" s="51">
         <v>19</v>
       </c>
@@ -5778,7 +5775,7 @@
         <v>17603.28</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="15.75">
+    <row r="28" spans="1:7" ht="15.6">
       <c r="A28" s="51">
         <v>20</v>
       </c>
@@ -5800,7 +5797,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="29" spans="1:7" ht="15.75">
+    <row r="29" spans="1:7" ht="15.6">
       <c r="A29" s="51">
         <v>21</v>
       </c>
@@ -5822,7 +5819,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="15.75">
+    <row r="30" spans="1:7" ht="15.6">
       <c r="A30" s="51">
         <v>22</v>
       </c>
@@ -5844,7 +5841,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="31" spans="1:7" ht="15.75">
+    <row r="31" spans="1:7" ht="15.6">
       <c r="A31" s="51">
         <v>23</v>
       </c>
@@ -5866,7 +5863,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="32" spans="1:7" ht="15.75">
+    <row r="32" spans="1:7" ht="15.6">
       <c r="A32" s="37"/>
       <c r="B32" s="52">
         <f>SUM(B9:B31)</f>
